--- a/AAII_Financials/Quarterly/ALBY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ALBY_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 

--- a/AAII_Financials/Quarterly/ALBY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ALBY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="92">
   <si>
     <t>ALBY</t>
   </si>
@@ -656,173 +656,180 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>39721</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>39629</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
         <v>2600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F8" s="3">
+        <v>2600</v>
+      </c>
+      <c r="G8" s="3">
         <v>2700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>2700</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J8" s="3">
         <v>2400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>1900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>1600</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L8" s="3">
-        <v>1800</v>
-      </c>
-      <c r="M8" s="3">
-        <v>1700</v>
+      <c r="M8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N8" s="3">
         <v>1800</v>
@@ -831,22 +838,22 @@
         <v>1700</v>
       </c>
       <c r="P8" s="3">
+        <v>1800</v>
+      </c>
+      <c r="Q8" s="3">
         <v>1700</v>
-      </c>
-      <c r="Q8" s="3">
-        <v>1800</v>
       </c>
       <c r="R8" s="3">
         <v>1700</v>
       </c>
-      <c r="S8" s="3" t="s">
-        <v>4</v>
+      <c r="S8" s="3">
+        <v>1800</v>
       </c>
       <c r="T8" s="3">
-        <v>0</v>
-      </c>
-      <c r="U8" s="3">
-        <v>0</v>
+        <v>1700</v>
+      </c>
+      <c r="U8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V8" s="3">
         <v>0</v>
@@ -857,11 +864,11 @@
       <c r="X8" s="3">
         <v>0</v>
       </c>
-      <c r="Y8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z8" s="3" t="s">
-        <v>4</v>
+      <c r="Y8" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="3">
+        <v>0</v>
       </c>
       <c r="AA8" s="3" t="s">
         <v>4</v>
@@ -875,14 +882,20 @@
       <c r="AD8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AE8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG8" s="3">
         <v>2400</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>2600</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -973,8 +986,14 @@
       <c r="AF9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1065,8 +1084,14 @@
       <c r="AF10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1099,8 +1124,10 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1191,8 +1218,14 @@
       <c r="AF12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1283,8 +1316,14 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1375,8 +1414,14 @@
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1449,11 +1494,11 @@
       <c r="Z15" s="3">
         <v>0</v>
       </c>
-      <c r="AA15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB15" s="3" t="s">
-        <v>4</v>
+      <c r="AA15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB15" s="3">
+        <v>0</v>
       </c>
       <c r="AC15" s="3" t="s">
         <v>4</v>
@@ -1467,8 +1512,14 @@
       <c r="AF15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1498,8 +1549,10 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1530,11 +1583,11 @@
       <c r="L17" s="3">
         <v>0</v>
       </c>
-      <c r="M17" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N17" s="3" t="s">
-        <v>4</v>
+      <c r="M17" s="3">
+        <v>0</v>
+      </c>
+      <c r="N17" s="3">
+        <v>0</v>
       </c>
       <c r="O17" s="3" t="s">
         <v>4</v>
@@ -1548,11 +1601,11 @@
       <c r="R17" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S17" s="3">
-        <v>0</v>
-      </c>
-      <c r="T17" s="3">
-        <v>0</v>
+      <c r="S17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T17" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U17" s="3">
         <v>0</v>
@@ -1566,11 +1619,11 @@
       <c r="X17" s="3">
         <v>0</v>
       </c>
-      <c r="Y17" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z17" s="3" t="s">
-        <v>4</v>
+      <c r="Y17" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z17" s="3">
+        <v>0</v>
       </c>
       <c r="AA17" s="3" t="s">
         <v>4</v>
@@ -1584,50 +1637,56 @@
       <c r="AD17" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AE17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG17" s="3">
         <v>3700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
         <v>2600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="E18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F18" s="3">
+        <v>2600</v>
+      </c>
+      <c r="G18" s="3">
         <v>2700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>2700</v>
       </c>
-      <c r="G18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J18" s="3">
         <v>2400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>1900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>1600</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N18" s="3">
         <v>1800</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O18" s="3" t="s">
         <v>4</v>
       </c>
@@ -1643,11 +1702,11 @@
       <c r="S18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T18" s="3">
-        <v>0</v>
-      </c>
-      <c r="U18" s="3">
-        <v>0</v>
+      <c r="T18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U18" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V18" s="3">
         <v>0</v>
@@ -1658,11 +1717,11 @@
       <c r="X18" s="3">
         <v>0</v>
       </c>
-      <c r="Y18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z18" s="3" t="s">
-        <v>4</v>
+      <c r="Y18" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z18" s="3">
+        <v>0</v>
       </c>
       <c r="AA18" s="3" t="s">
         <v>4</v>
@@ -1676,14 +1735,20 @@
       <c r="AD18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AE18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG18" s="3">
         <v>-1300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1716,34 +1781,36 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
         <v>-1300</v>
       </c>
-      <c r="E20" s="3">
-        <v>-1300</v>
+      <c r="E20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F20" s="3">
         <v>-1300</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>4</v>
+      <c r="G20" s="3">
+        <v>-1300</v>
       </c>
       <c r="H20" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J20" s="3">
         <v>-1400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-1100</v>
-      </c>
-      <c r="J20" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>4</v>
       </c>
       <c r="L20" s="3">
         <v>-1100</v>
@@ -1751,8 +1818,8 @@
       <c r="M20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N20" s="3" t="s">
-        <v>4</v>
+      <c r="N20" s="3">
+        <v>-1100</v>
       </c>
       <c r="O20" s="3" t="s">
         <v>4</v>
@@ -1769,11 +1836,11 @@
       <c r="S20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T20" s="3">
-        <v>500</v>
-      </c>
-      <c r="U20" s="3">
-        <v>500</v>
+      <c r="T20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V20" s="3">
         <v>500</v>
@@ -1784,11 +1851,11 @@
       <c r="X20" s="3">
         <v>500</v>
       </c>
-      <c r="Y20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z20" s="3" t="s">
-        <v>4</v>
+      <c r="Y20" s="3">
+        <v>500</v>
+      </c>
+      <c r="Z20" s="3">
+        <v>500</v>
       </c>
       <c r="AA20" s="3" t="s">
         <v>4</v>
@@ -1802,14 +1869,20 @@
       <c r="AD20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AE20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG20" s="3">
         <v>-3400</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AH20" s="3">
         <v>-1700</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1900,8 +1973,14 @@
       <c r="AF21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1992,8 +2071,14 @@
       <c r="AF22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2001,55 +2086,55 @@
         <v>1300</v>
       </c>
       <c r="E23" s="3">
-        <v>1400</v>
+        <v>1200</v>
       </c>
       <c r="F23" s="3">
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="G23" s="3">
         <v>1400</v>
       </c>
       <c r="H23" s="3">
+        <v>1400</v>
+      </c>
+      <c r="I23" s="3">
+        <v>1400</v>
+      </c>
+      <c r="J23" s="3">
         <v>1000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>2500</v>
-      </c>
-      <c r="L23" s="3">
-        <v>700</v>
-      </c>
-      <c r="M23" s="3">
-        <v>600</v>
       </c>
       <c r="N23" s="3">
         <v>700</v>
       </c>
       <c r="O23" s="3">
+        <v>600</v>
+      </c>
+      <c r="P23" s="3">
+        <v>700</v>
+      </c>
+      <c r="Q23" s="3">
         <v>500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>700</v>
-      </c>
-      <c r="R23" s="3">
-        <v>500</v>
-      </c>
-      <c r="S23" s="3">
-        <v>300</v>
       </c>
       <c r="T23" s="3">
         <v>500</v>
       </c>
       <c r="U23" s="3">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="V23" s="3">
         <v>500</v>
@@ -2061,31 +2146,37 @@
         <v>500</v>
       </c>
       <c r="Y23" s="3">
+        <v>500</v>
+      </c>
+      <c r="Z23" s="3">
+        <v>500</v>
+      </c>
+      <c r="AA23" s="3">
         <v>300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>400</v>
       </c>
-      <c r="AB23" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC23" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AD23" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AE23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG23" s="3">
         <v>-4700</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2093,40 +2184,40 @@
         <v>300</v>
       </c>
       <c r="E24" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="F24" s="3">
         <v>300</v>
       </c>
       <c r="G24" s="3">
+        <v>400</v>
+      </c>
+      <c r="H24" s="3">
         <v>300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
+        <v>300</v>
+      </c>
+      <c r="J24" s="3">
         <v>200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>200</v>
-      </c>
-      <c r="J24" s="3">
-        <v>100</v>
-      </c>
-      <c r="K24" s="3">
-        <v>600</v>
       </c>
       <c r="L24" s="3">
         <v>100</v>
       </c>
       <c r="M24" s="3">
+        <v>600</v>
+      </c>
+      <c r="N24" s="3">
         <v>100</v>
-      </c>
-      <c r="N24" s="3">
-        <v>200</v>
       </c>
       <c r="O24" s="3">
         <v>100</v>
       </c>
       <c r="P24" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Q24" s="3">
         <v>100</v>
@@ -2159,25 +2250,31 @@
         <v>100</v>
       </c>
       <c r="AA24" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB24" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC24" s="3">
         <v>2500</v>
       </c>
-      <c r="AB24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC24" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AD24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AE24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG24" s="3">
         <v>-1600</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AH24" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2268,64 +2365,70 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
         <v>1000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="E26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F26" s="3">
+        <v>1000</v>
+      </c>
+      <c r="G26" s="3">
         <v>1100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>1100</v>
       </c>
-      <c r="G26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J26" s="3">
         <v>800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>400</v>
       </c>
-      <c r="K26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N26" s="3">
         <v>500</v>
-      </c>
-      <c r="M26" s="3">
-        <v>400</v>
-      </c>
-      <c r="N26" s="3">
-        <v>600</v>
       </c>
       <c r="O26" s="3">
         <v>400</v>
       </c>
       <c r="P26" s="3">
+        <v>600</v>
+      </c>
+      <c r="Q26" s="3">
         <v>400</v>
-      </c>
-      <c r="Q26" s="3">
-        <v>500</v>
       </c>
       <c r="R26" s="3">
         <v>400</v>
       </c>
-      <c r="S26" s="3" t="s">
-        <v>4</v>
+      <c r="S26" s="3">
+        <v>500</v>
       </c>
       <c r="T26" s="3">
-        <v>0</v>
-      </c>
-      <c r="U26" s="3">
-        <v>0</v>
+        <v>400</v>
+      </c>
+      <c r="U26" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V26" s="3">
         <v>0</v>
@@ -2336,11 +2439,11 @@
       <c r="X26" s="3">
         <v>0</v>
       </c>
-      <c r="Y26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z26" s="3" t="s">
-        <v>4</v>
+      <c r="Y26" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z26" s="3">
+        <v>0</v>
       </c>
       <c r="AA26" s="3" t="s">
         <v>4</v>
@@ -2354,70 +2457,76 @@
       <c r="AD26" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AE26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG26" s="3">
         <v>-3100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
         <v>1000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="E27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F27" s="3">
+        <v>1000</v>
+      </c>
+      <c r="G27" s="3">
         <v>1100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>1100</v>
       </c>
-      <c r="G27" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J27" s="3">
         <v>800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>400</v>
       </c>
-      <c r="K27" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N27" s="3">
         <v>500</v>
-      </c>
-      <c r="M27" s="3">
-        <v>400</v>
-      </c>
-      <c r="N27" s="3">
-        <v>600</v>
       </c>
       <c r="O27" s="3">
         <v>400</v>
       </c>
       <c r="P27" s="3">
+        <v>600</v>
+      </c>
+      <c r="Q27" s="3">
         <v>400</v>
-      </c>
-      <c r="Q27" s="3">
-        <v>500</v>
       </c>
       <c r="R27" s="3">
         <v>400</v>
       </c>
-      <c r="S27" s="3" t="s">
-        <v>4</v>
+      <c r="S27" s="3">
+        <v>500</v>
       </c>
       <c r="T27" s="3">
-        <v>0</v>
-      </c>
-      <c r="U27" s="3">
-        <v>0</v>
+        <v>400</v>
+      </c>
+      <c r="U27" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V27" s="3">
         <v>0</v>
@@ -2428,11 +2537,11 @@
       <c r="X27" s="3">
         <v>0</v>
       </c>
-      <c r="Y27" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z27" s="3" t="s">
-        <v>4</v>
+      <c r="Y27" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z27" s="3">
+        <v>0</v>
       </c>
       <c r="AA27" s="3" t="s">
         <v>4</v>
@@ -2446,14 +2555,20 @@
       <c r="AD27" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AE27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG27" s="3">
         <v>-3100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2544,8 +2659,14 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2636,8 +2757,14 @@
       <c r="AF29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2728,8 +2855,14 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2820,34 +2953,40 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
         <v>1300</v>
       </c>
-      <c r="E32" s="3">
-        <v>1300</v>
+      <c r="E32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F32" s="3">
         <v>1300</v>
       </c>
-      <c r="G32" s="3" t="s">
-        <v>4</v>
+      <c r="G32" s="3">
+        <v>1300</v>
       </c>
       <c r="H32" s="3">
+        <v>1300</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J32" s="3">
         <v>1400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>1100</v>
-      </c>
-      <c r="J32" s="3">
-        <v>1100</v>
-      </c>
-      <c r="K32" s="3" t="s">
-        <v>4</v>
       </c>
       <c r="L32" s="3">
         <v>1100</v>
@@ -2855,8 +2994,8 @@
       <c r="M32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N32" s="3" t="s">
-        <v>4</v>
+      <c r="N32" s="3">
+        <v>1100</v>
       </c>
       <c r="O32" s="3" t="s">
         <v>4</v>
@@ -2873,11 +3012,11 @@
       <c r="S32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T32" s="3">
-        <v>-500</v>
-      </c>
-      <c r="U32" s="3">
-        <v>-500</v>
+      <c r="T32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V32" s="3">
         <v>-500</v>
@@ -2888,11 +3027,11 @@
       <c r="X32" s="3">
         <v>-500</v>
       </c>
-      <c r="Y32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z32" s="3" t="s">
-        <v>4</v>
+      <c r="Y32" s="3">
+        <v>-500</v>
+      </c>
+      <c r="Z32" s="3">
+        <v>-500</v>
       </c>
       <c r="AA32" s="3" t="s">
         <v>4</v>
@@ -2906,70 +3045,76 @@
       <c r="AD32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AE32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG32" s="3">
         <v>3400</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AH32" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
         <v>1000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="E33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F33" s="3">
+        <v>1000</v>
+      </c>
+      <c r="G33" s="3">
         <v>1100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>1100</v>
       </c>
-      <c r="G33" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J33" s="3">
         <v>800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>400</v>
       </c>
-      <c r="K33" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N33" s="3">
         <v>500</v>
-      </c>
-      <c r="M33" s="3">
-        <v>400</v>
-      </c>
-      <c r="N33" s="3">
-        <v>600</v>
       </c>
       <c r="O33" s="3">
         <v>400</v>
       </c>
       <c r="P33" s="3">
+        <v>600</v>
+      </c>
+      <c r="Q33" s="3">
         <v>400</v>
-      </c>
-      <c r="Q33" s="3">
-        <v>500</v>
       </c>
       <c r="R33" s="3">
         <v>400</v>
       </c>
-      <c r="S33" s="3" t="s">
-        <v>4</v>
+      <c r="S33" s="3">
+        <v>500</v>
       </c>
       <c r="T33" s="3">
-        <v>0</v>
-      </c>
-      <c r="U33" s="3">
-        <v>0</v>
+        <v>400</v>
+      </c>
+      <c r="U33" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V33" s="3">
         <v>0</v>
@@ -2980,11 +3125,11 @@
       <c r="X33" s="3">
         <v>0</v>
       </c>
-      <c r="Y33" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z33" s="3" t="s">
-        <v>4</v>
+      <c r="Y33" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z33" s="3">
+        <v>0</v>
       </c>
       <c r="AA33" s="3" t="s">
         <v>4</v>
@@ -2998,14 +3143,20 @@
       <c r="AD33" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AE33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG33" s="3">
         <v>-3100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3096,64 +3247,70 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
         <v>1000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="E35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F35" s="3">
+        <v>1000</v>
+      </c>
+      <c r="G35" s="3">
         <v>1100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>1100</v>
       </c>
-      <c r="G35" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J35" s="3">
         <v>800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>400</v>
       </c>
-      <c r="K35" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N35" s="3">
         <v>500</v>
-      </c>
-      <c r="M35" s="3">
-        <v>400</v>
-      </c>
-      <c r="N35" s="3">
-        <v>600</v>
       </c>
       <c r="O35" s="3">
         <v>400</v>
       </c>
       <c r="P35" s="3">
+        <v>600</v>
+      </c>
+      <c r="Q35" s="3">
         <v>400</v>
-      </c>
-      <c r="Q35" s="3">
-        <v>500</v>
       </c>
       <c r="R35" s="3">
         <v>400</v>
       </c>
-      <c r="S35" s="3" t="s">
-        <v>4</v>
+      <c r="S35" s="3">
+        <v>500</v>
       </c>
       <c r="T35" s="3">
-        <v>0</v>
-      </c>
-      <c r="U35" s="3">
-        <v>0</v>
+        <v>400</v>
+      </c>
+      <c r="U35" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V35" s="3">
         <v>0</v>
@@ -3164,11 +3321,11 @@
       <c r="X35" s="3">
         <v>0</v>
       </c>
-      <c r="Y35" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z35" s="3" t="s">
-        <v>4</v>
+      <c r="Y35" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z35" s="3">
+        <v>0</v>
       </c>
       <c r="AA35" s="3" t="s">
         <v>4</v>
@@ -3182,111 +3339,123 @@
       <c r="AD35" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AE35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG35" s="3">
         <v>-3100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>39721</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>39629</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3319,8 +3488,10 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3353,8 +3524,10 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -3440,13 +3613,19 @@
         <v>0</v>
       </c>
       <c r="AE41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG41" s="3">
         <v>4100</v>
       </c>
-      <c r="AF41" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AH41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3532,13 +3711,19 @@
         <v>0</v>
       </c>
       <c r="AE42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG42" s="3">
         <v>900</v>
       </c>
-      <c r="AF42" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3629,8 +3814,14 @@
       <c r="AF43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3721,8 +3912,14 @@
       <c r="AF44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3813,8 +4010,14 @@
       <c r="AF45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3905,8 +4108,14 @@
       <c r="AF46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3997,8 +4206,14 @@
       <c r="AF47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4084,13 +4299,19 @@
         <v>0</v>
       </c>
       <c r="AE48" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF48" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG48" s="3">
         <v>6400</v>
       </c>
-      <c r="AF48" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AH48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4176,13 +4397,19 @@
         <v>0</v>
       </c>
       <c r="AE49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG49" s="3">
         <v>2500</v>
       </c>
-      <c r="AF49" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AH49" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4273,8 +4500,14 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4365,8 +4598,14 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4457,8 +4696,14 @@
       <c r="AF52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4549,8 +4794,14 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
@@ -4636,13 +4887,19 @@
         <v>0</v>
       </c>
       <c r="AE54" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF54" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG54" s="3">
         <v>198900</v>
       </c>
-      <c r="AF54" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AH54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4675,8 +4932,10 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4709,8 +4968,10 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4801,8 +5062,14 @@
       <c r="AF57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4893,8 +5160,14 @@
       <c r="AF58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4985,8 +5258,14 @@
       <c r="AF59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5077,8 +5356,14 @@
       <c r="AF60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG60" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5169,8 +5454,14 @@
       <c r="AF61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5261,8 +5552,14 @@
       <c r="AF62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5353,8 +5650,14 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5445,8 +5748,14 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5537,8 +5846,14 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
@@ -5624,13 +5939,19 @@
         <v>0</v>
       </c>
       <c r="AE66" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF66" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG66" s="3">
         <v>177800</v>
       </c>
-      <c r="AF66" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AH66" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5663,8 +5984,10 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5755,8 +6078,14 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5847,8 +6176,14 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5939,8 +6274,14 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6031,8 +6372,14 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -6123,8 +6470,14 @@
       <c r="AF72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG72" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6215,8 +6568,14 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6307,8 +6666,14 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6399,62 +6764,68 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>25900</v>
+      </c>
+      <c r="E76" s="3">
+        <v>23200</v>
+      </c>
+      <c r="F76" s="3">
         <v>23700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>23600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>22800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>20800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>21000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>20500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>20400</v>
-      </c>
-      <c r="K76" s="3">
-        <v>19100</v>
-      </c>
-      <c r="L76" s="3">
-        <v>19600</v>
       </c>
       <c r="M76" s="3">
         <v>19100</v>
       </c>
       <c r="N76" s="3">
+        <v>19600</v>
+      </c>
+      <c r="O76" s="3">
+        <v>19100</v>
+      </c>
+      <c r="P76" s="3">
         <v>18600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>17000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>16800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>17100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>16600</v>
       </c>
-      <c r="S76" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U76" s="3" t="s">
         <v>4</v>
       </c>
@@ -6464,11 +6835,11 @@
       <c r="W76" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X76" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y76" s="3">
-        <v>0</v>
+      <c r="X76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y76" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Z76" s="3">
         <v>0</v>
@@ -6486,13 +6857,19 @@
         <v>0</v>
       </c>
       <c r="AE76" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF76" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG76" s="3">
         <v>21100</v>
       </c>
-      <c r="AF76" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AH76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6583,161 +6960,173 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>39721</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>39629</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
         <v>1000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="E81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F81" s="3">
+        <v>1000</v>
+      </c>
+      <c r="G81" s="3">
         <v>1100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>1100</v>
       </c>
-      <c r="G81" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J81" s="3">
         <v>800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>400</v>
       </c>
-      <c r="K81" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N81" s="3">
         <v>500</v>
-      </c>
-      <c r="M81" s="3">
-        <v>400</v>
-      </c>
-      <c r="N81" s="3">
-        <v>600</v>
       </c>
       <c r="O81" s="3">
         <v>400</v>
       </c>
       <c r="P81" s="3">
+        <v>600</v>
+      </c>
+      <c r="Q81" s="3">
         <v>400</v>
-      </c>
-      <c r="Q81" s="3">
-        <v>500</v>
       </c>
       <c r="R81" s="3">
         <v>400</v>
       </c>
-      <c r="S81" s="3" t="s">
-        <v>4</v>
+      <c r="S81" s="3">
+        <v>500</v>
       </c>
       <c r="T81" s="3">
-        <v>0</v>
-      </c>
-      <c r="U81" s="3">
-        <v>0</v>
+        <v>400</v>
+      </c>
+      <c r="U81" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V81" s="3">
         <v>0</v>
@@ -6748,11 +7137,11 @@
       <c r="X81" s="3">
         <v>0</v>
       </c>
-      <c r="Y81" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z81" s="3" t="s">
-        <v>4</v>
+      <c r="Y81" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z81" s="3">
+        <v>0</v>
       </c>
       <c r="AA81" s="3" t="s">
         <v>4</v>
@@ -6766,14 +7155,20 @@
       <c r="AD81" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AE81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG81" s="3">
         <v>-3100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6806,8 +7201,10 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6898,8 +7295,14 @@
       <c r="AF83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6990,8 +7393,14 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7082,8 +7491,14 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7174,8 +7589,14 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7266,8 +7687,14 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7358,8 +7785,14 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -7450,8 +7883,14 @@
       <c r="AF89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7484,8 +7923,10 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7576,8 +8017,14 @@
       <c r="AF91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7668,8 +8115,14 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7760,8 +8213,14 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -7852,8 +8311,14 @@
       <c r="AF94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7886,8 +8351,10 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7978,8 +8445,14 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8070,8 +8543,14 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8162,8 +8641,14 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8254,8 +8739,14 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8346,8 +8837,14 @@
       <c r="AF100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8438,8 +8935,14 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -8528,6 +9031,12 @@
         <v>0</v>
       </c>
       <c r="AF102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ALBY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ALBY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="92">
   <si>
     <t>ALBY</t>
   </si>
@@ -656,207 +656,211 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>39721</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>39629</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E8" s="3">
         <v>2600</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F8" s="3">
+      <c r="F8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G8" s="3">
         <v>2600</v>
-      </c>
-      <c r="G8" s="3">
-        <v>2700</v>
       </c>
       <c r="H8" s="3">
         <v>2700</v>
       </c>
-      <c r="I8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J8" s="3">
+      <c r="I8" s="3">
+        <v>2700</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K8" s="3">
         <v>2400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1600</v>
       </c>
-      <c r="M8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N8" s="3">
+      <c r="N8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O8" s="3">
         <v>1800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1800</v>
-      </c>
-      <c r="Q8" s="3">
-        <v>1700</v>
       </c>
       <c r="R8" s="3">
         <v>1700</v>
       </c>
       <c r="S8" s="3">
+        <v>1700</v>
+      </c>
+      <c r="T8" s="3">
         <v>1800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1700</v>
       </c>
-      <c r="U8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V8" s="3">
-        <v>0</v>
+      <c r="V8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W8" s="3">
         <v>0</v>
@@ -870,8 +874,8 @@
       <c r="Z8" s="3">
         <v>0</v>
       </c>
-      <c r="AA8" s="3" t="s">
-        <v>4</v>
+      <c r="AA8" s="3">
+        <v>0</v>
       </c>
       <c r="AB8" s="3" t="s">
         <v>4</v>
@@ -888,14 +892,17 @@
       <c r="AF8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AG8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH8" s="3">
         <v>2400</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2600</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -992,8 +999,11 @@
       <c r="AH9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1090,8 +1100,11 @@
       <c r="AH10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1126,8 +1139,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1224,8 +1238,11 @@
       <c r="AH12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1322,8 +1339,11 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1420,8 +1440,11 @@
       <c r="AH14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1500,8 +1523,8 @@
       <c r="AB15" s="3">
         <v>0</v>
       </c>
-      <c r="AC15" s="3" t="s">
-        <v>4</v>
+      <c r="AC15" s="3">
+        <v>0</v>
       </c>
       <c r="AD15" s="3" t="s">
         <v>4</v>
@@ -1518,8 +1541,11 @@
       <c r="AH15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1551,8 +1577,9 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1589,8 +1616,8 @@
       <c r="N17" s="3">
         <v>0</v>
       </c>
-      <c r="O17" s="3" t="s">
-        <v>4</v>
+      <c r="O17" s="3">
+        <v>0</v>
       </c>
       <c r="P17" s="3" t="s">
         <v>4</v>
@@ -1607,8 +1634,8 @@
       <c r="T17" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U17" s="3">
-        <v>0</v>
+      <c r="U17" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V17" s="3">
         <v>0</v>
@@ -1625,8 +1652,8 @@
       <c r="Z17" s="3">
         <v>0</v>
       </c>
-      <c r="AA17" s="3" t="s">
-        <v>4</v>
+      <c r="AA17" s="3">
+        <v>0</v>
       </c>
       <c r="AB17" s="3" t="s">
         <v>4</v>
@@ -1643,53 +1670,56 @@
       <c r="AF17" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AG17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH17" s="3">
         <v>3700</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E18" s="3">
         <v>2600</v>
       </c>
-      <c r="E18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F18" s="3">
+      <c r="F18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G18" s="3">
         <v>2600</v>
-      </c>
-      <c r="G18" s="3">
-        <v>2700</v>
       </c>
       <c r="H18" s="3">
         <v>2700</v>
       </c>
-      <c r="I18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J18" s="3">
+      <c r="I18" s="3">
+        <v>2700</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K18" s="3">
         <v>2400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1600</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N18" s="3">
+      <c r="N18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O18" s="3">
         <v>1800</v>
       </c>
-      <c r="O18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P18" s="3" t="s">
         <v>4</v>
       </c>
@@ -1708,8 +1738,8 @@
       <c r="U18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V18" s="3">
-        <v>0</v>
+      <c r="V18" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W18" s="3">
         <v>0</v>
@@ -1723,8 +1753,8 @@
       <c r="Z18" s="3">
         <v>0</v>
       </c>
-      <c r="AA18" s="3" t="s">
-        <v>4</v>
+      <c r="AA18" s="3">
+        <v>0</v>
       </c>
       <c r="AB18" s="3" t="s">
         <v>4</v>
@@ -1741,14 +1771,17 @@
       <c r="AF18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AG18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH18" s="3">
         <v>-1300</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1783,19 +1816,20 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E20" s="3">
         <v>-1300</v>
       </c>
-      <c r="E20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F20" s="3">
-        <v>-1300</v>
+      <c r="F20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G20" s="3">
         <v>-1300</v>
@@ -1803,26 +1837,26 @@
       <c r="H20" s="3">
         <v>-1300</v>
       </c>
-      <c r="I20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J20" s="3">
+      <c r="I20" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K20" s="3">
         <v>-1400</v>
-      </c>
-      <c r="K20" s="3">
-        <v>-1100</v>
       </c>
       <c r="L20" s="3">
         <v>-1100</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N20" s="3">
+      <c r="M20" s="3">
         <v>-1100</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>4</v>
+      <c r="N20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O20" s="3">
+        <v>-1100</v>
       </c>
       <c r="P20" s="3" t="s">
         <v>4</v>
@@ -1842,8 +1876,8 @@
       <c r="U20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V20" s="3">
-        <v>500</v>
+      <c r="V20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W20" s="3">
         <v>500</v>
@@ -1857,8 +1891,8 @@
       <c r="Z20" s="3">
         <v>500</v>
       </c>
-      <c r="AA20" s="3" t="s">
-        <v>4</v>
+      <c r="AA20" s="3">
+        <v>500</v>
       </c>
       <c r="AB20" s="3" t="s">
         <v>4</v>
@@ -1875,14 +1909,17 @@
       <c r="AF20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AG20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH20" s="3">
         <v>-3400</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-1700</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1979,8 +2016,11 @@
       <c r="AH21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2077,22 +2117,25 @@
       <c r="AH22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E23" s="3">
         <v>1300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1300</v>
-      </c>
-      <c r="G23" s="3">
-        <v>1400</v>
       </c>
       <c r="H23" s="3">
         <v>1400</v>
@@ -2101,43 +2144,43 @@
         <v>1400</v>
       </c>
       <c r="J23" s="3">
+        <v>1400</v>
+      </c>
+      <c r="K23" s="3">
         <v>1000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>2500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>300</v>
-      </c>
-      <c r="V23" s="3">
-        <v>500</v>
       </c>
       <c r="W23" s="3">
         <v>500</v>
@@ -2152,36 +2195,39 @@
         <v>500</v>
       </c>
       <c r="AA23" s="3">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="AB23" s="3">
         <v>300</v>
       </c>
       <c r="AC23" s="3">
+        <v>300</v>
+      </c>
+      <c r="AD23" s="3">
         <v>400</v>
       </c>
-      <c r="AD23" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE23" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AF23" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AG23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH23" s="3">
         <v>-4700</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="E24" s="3">
         <v>300</v>
@@ -2190,37 +2236,37 @@
         <v>300</v>
       </c>
       <c r="G24" s="3">
+        <v>300</v>
+      </c>
+      <c r="H24" s="3">
         <v>400</v>
-      </c>
-      <c r="H24" s="3">
-        <v>300</v>
       </c>
       <c r="I24" s="3">
         <v>300</v>
       </c>
       <c r="J24" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="K24" s="3">
         <v>200</v>
       </c>
       <c r="L24" s="3">
+        <v>200</v>
+      </c>
+      <c r="M24" s="3">
         <v>100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>600</v>
-      </c>
-      <c r="N24" s="3">
-        <v>100</v>
       </c>
       <c r="O24" s="3">
         <v>100</v>
       </c>
       <c r="P24" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q24" s="3">
         <v>200</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>100</v>
       </c>
       <c r="R24" s="3">
         <v>100</v>
@@ -2256,25 +2302,28 @@
         <v>100</v>
       </c>
       <c r="AC24" s="3">
+        <v>100</v>
+      </c>
+      <c r="AD24" s="3">
         <v>2500</v>
       </c>
-      <c r="AD24" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE24" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AF24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AG24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH24" s="3">
         <v>-1600</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2371,67 +2420,70 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E26" s="3">
         <v>1000</v>
       </c>
-      <c r="E26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F26" s="3">
+      <c r="F26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G26" s="3">
         <v>1000</v>
-      </c>
-      <c r="G26" s="3">
-        <v>1100</v>
       </c>
       <c r="H26" s="3">
         <v>1100</v>
       </c>
-      <c r="I26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J26" s="3">
+      <c r="I26" s="3">
+        <v>1100</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K26" s="3">
         <v>800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>400</v>
       </c>
-      <c r="M26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N26" s="3">
+      <c r="N26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O26" s="3">
         <v>500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>600</v>
-      </c>
-      <c r="Q26" s="3">
-        <v>400</v>
       </c>
       <c r="R26" s="3">
         <v>400</v>
       </c>
       <c r="S26" s="3">
+        <v>400</v>
+      </c>
+      <c r="T26" s="3">
         <v>500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>400</v>
       </c>
-      <c r="U26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V26" s="3">
-        <v>0</v>
+      <c r="V26" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W26" s="3">
         <v>0</v>
@@ -2445,8 +2497,8 @@
       <c r="Z26" s="3">
         <v>0</v>
       </c>
-      <c r="AA26" s="3" t="s">
-        <v>4</v>
+      <c r="AA26" s="3">
+        <v>0</v>
       </c>
       <c r="AB26" s="3" t="s">
         <v>4</v>
@@ -2463,73 +2515,76 @@
       <c r="AF26" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AG26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH26" s="3">
         <v>-3100</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E27" s="3">
         <v>1000</v>
       </c>
-      <c r="E27" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F27" s="3">
+      <c r="F27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G27" s="3">
         <v>1000</v>
-      </c>
-      <c r="G27" s="3">
-        <v>1100</v>
       </c>
       <c r="H27" s="3">
         <v>1100</v>
       </c>
-      <c r="I27" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J27" s="3">
+      <c r="I27" s="3">
+        <v>1100</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K27" s="3">
         <v>800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>400</v>
       </c>
-      <c r="M27" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N27" s="3">
+      <c r="N27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O27" s="3">
         <v>500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>600</v>
-      </c>
-      <c r="Q27" s="3">
-        <v>400</v>
       </c>
       <c r="R27" s="3">
         <v>400</v>
       </c>
       <c r="S27" s="3">
+        <v>400</v>
+      </c>
+      <c r="T27" s="3">
         <v>500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>400</v>
       </c>
-      <c r="U27" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V27" s="3">
-        <v>0</v>
+      <c r="V27" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W27" s="3">
         <v>0</v>
@@ -2543,8 +2598,8 @@
       <c r="Z27" s="3">
         <v>0</v>
       </c>
-      <c r="AA27" s="3" t="s">
-        <v>4</v>
+      <c r="AA27" s="3">
+        <v>0</v>
       </c>
       <c r="AB27" s="3" t="s">
         <v>4</v>
@@ -2561,14 +2616,17 @@
       <c r="AF27" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AG27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH27" s="3">
         <v>-3100</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2665,8 +2723,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2763,8 +2824,11 @@
       <c r="AH29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2861,8 +2925,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2959,19 +3026,22 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E32" s="3">
         <v>1300</v>
       </c>
-      <c r="E32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F32" s="3">
-        <v>1300</v>
+      <c r="F32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G32" s="3">
         <v>1300</v>
@@ -2979,26 +3049,26 @@
       <c r="H32" s="3">
         <v>1300</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J32" s="3">
+      <c r="I32" s="3">
+        <v>1300</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K32" s="3">
         <v>1400</v>
-      </c>
-      <c r="K32" s="3">
-        <v>1100</v>
       </c>
       <c r="L32" s="3">
         <v>1100</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N32" s="3">
+      <c r="M32" s="3">
         <v>1100</v>
       </c>
-      <c r="O32" s="3" t="s">
-        <v>4</v>
+      <c r="N32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O32" s="3">
+        <v>1100</v>
       </c>
       <c r="P32" s="3" t="s">
         <v>4</v>
@@ -3018,8 +3088,8 @@
       <c r="U32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V32" s="3">
-        <v>-500</v>
+      <c r="V32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W32" s="3">
         <v>-500</v>
@@ -3033,8 +3103,8 @@
       <c r="Z32" s="3">
         <v>-500</v>
       </c>
-      <c r="AA32" s="3" t="s">
-        <v>4</v>
+      <c r="AA32" s="3">
+        <v>-500</v>
       </c>
       <c r="AB32" s="3" t="s">
         <v>4</v>
@@ -3051,73 +3121,76 @@
       <c r="AF32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AG32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH32" s="3">
         <v>3400</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E33" s="3">
         <v>1000</v>
       </c>
-      <c r="E33" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F33" s="3">
+      <c r="F33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G33" s="3">
         <v>1000</v>
-      </c>
-      <c r="G33" s="3">
-        <v>1100</v>
       </c>
       <c r="H33" s="3">
         <v>1100</v>
       </c>
-      <c r="I33" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J33" s="3">
+      <c r="I33" s="3">
+        <v>1100</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K33" s="3">
         <v>800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>400</v>
       </c>
-      <c r="M33" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N33" s="3">
+      <c r="N33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O33" s="3">
         <v>500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>600</v>
-      </c>
-      <c r="Q33" s="3">
-        <v>400</v>
       </c>
       <c r="R33" s="3">
         <v>400</v>
       </c>
       <c r="S33" s="3">
+        <v>400</v>
+      </c>
+      <c r="T33" s="3">
         <v>500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>400</v>
       </c>
-      <c r="U33" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V33" s="3">
-        <v>0</v>
+      <c r="V33" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W33" s="3">
         <v>0</v>
@@ -3131,8 +3204,8 @@
       <c r="Z33" s="3">
         <v>0</v>
       </c>
-      <c r="AA33" s="3" t="s">
-        <v>4</v>
+      <c r="AA33" s="3">
+        <v>0</v>
       </c>
       <c r="AB33" s="3" t="s">
         <v>4</v>
@@ -3149,14 +3222,17 @@
       <c r="AF33" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AG33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH33" s="3">
         <v>-3100</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3253,67 +3329,70 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E35" s="3">
         <v>1000</v>
       </c>
-      <c r="E35" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F35" s="3">
+      <c r="F35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G35" s="3">
         <v>1000</v>
-      </c>
-      <c r="G35" s="3">
-        <v>1100</v>
       </c>
       <c r="H35" s="3">
         <v>1100</v>
       </c>
-      <c r="I35" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J35" s="3">
+      <c r="I35" s="3">
+        <v>1100</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K35" s="3">
         <v>800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>400</v>
       </c>
-      <c r="M35" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N35" s="3">
+      <c r="N35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O35" s="3">
         <v>500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>600</v>
-      </c>
-      <c r="Q35" s="3">
-        <v>400</v>
       </c>
       <c r="R35" s="3">
         <v>400</v>
       </c>
       <c r="S35" s="3">
+        <v>400</v>
+      </c>
+      <c r="T35" s="3">
         <v>500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>400</v>
       </c>
-      <c r="U35" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V35" s="3">
-        <v>0</v>
+      <c r="V35" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W35" s="3">
         <v>0</v>
@@ -3327,8 +3406,8 @@
       <c r="Z35" s="3">
         <v>0</v>
       </c>
-      <c r="AA35" s="3" t="s">
-        <v>4</v>
+      <c r="AA35" s="3">
+        <v>0</v>
       </c>
       <c r="AB35" s="3" t="s">
         <v>4</v>
@@ -3345,117 +3424,123 @@
       <c r="AF35" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AG35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH35" s="3">
         <v>-3100</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>39721</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>39629</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3490,8 +3575,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3526,8 +3612,9 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -3619,13 +3706,16 @@
         <v>0</v>
       </c>
       <c r="AG41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH41" s="3">
         <v>4100</v>
       </c>
-      <c r="AH41" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3717,13 +3807,16 @@
         <v>0</v>
       </c>
       <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH42" s="3">
         <v>900</v>
       </c>
-      <c r="AH42" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3820,8 +3913,11 @@
       <c r="AH43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3918,8 +4014,11 @@
       <c r="AH44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4016,8 +4115,11 @@
       <c r="AH45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -4114,8 +4216,11 @@
       <c r="AH46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4212,8 +4317,11 @@
       <c r="AH47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4305,13 +4413,16 @@
         <v>0</v>
       </c>
       <c r="AG48" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH48" s="3">
         <v>6400</v>
       </c>
-      <c r="AH48" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4403,13 +4514,16 @@
         <v>0</v>
       </c>
       <c r="AG49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH49" s="3">
         <v>2500</v>
       </c>
-      <c r="AH49" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI49" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4506,8 +4620,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4604,8 +4721,11 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4702,8 +4822,11 @@
       <c r="AH52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4800,8 +4923,11 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
@@ -4893,13 +5019,16 @@
         <v>0</v>
       </c>
       <c r="AG54" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH54" s="3">
         <v>198900</v>
       </c>
-      <c r="AH54" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4934,8 +5063,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4970,8 +5100,9 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -5068,8 +5199,11 @@
       <c r="AH57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5166,8 +5300,11 @@
       <c r="AH58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5264,8 +5401,11 @@
       <c r="AH59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5362,8 +5502,11 @@
       <c r="AH60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5460,8 +5603,11 @@
       <c r="AH61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5558,8 +5704,11 @@
       <c r="AH62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5656,8 +5805,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5754,8 +5906,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5852,8 +6007,11 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
@@ -5945,13 +6103,16 @@
         <v>0</v>
       </c>
       <c r="AG66" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH66" s="3">
         <v>177800</v>
       </c>
-      <c r="AH66" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI66" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5986,8 +6147,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6084,8 +6246,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6182,8 +6347,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6280,8 +6448,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6378,8 +6549,11 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -6476,8 +6650,11 @@
       <c r="AH72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6574,8 +6751,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6672,8 +6852,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6770,65 +6953,68 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>26100</v>
+      </c>
+      <c r="E76" s="3">
         <v>25900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>23200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>23700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>23600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>22800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>20800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>21000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>20500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>20400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>19100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>19600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>19100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>18600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>17000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>16800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>17100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>16600</v>
       </c>
-      <c r="U76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V76" s="3" t="s">
         <v>4</v>
       </c>
@@ -6841,8 +7027,8 @@
       <c r="Y76" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z76" s="3">
-        <v>0</v>
+      <c r="Z76" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AA76" s="3">
         <v>0</v>
@@ -6863,13 +7049,16 @@
         <v>0</v>
       </c>
       <c r="AG76" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH76" s="3">
         <v>21100</v>
       </c>
-      <c r="AH76" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6966,170 +7155,176 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>39721</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>39629</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E81" s="3">
         <v>1000</v>
       </c>
-      <c r="E81" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F81" s="3">
+      <c r="F81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G81" s="3">
         <v>1000</v>
-      </c>
-      <c r="G81" s="3">
-        <v>1100</v>
       </c>
       <c r="H81" s="3">
         <v>1100</v>
       </c>
-      <c r="I81" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J81" s="3">
+      <c r="I81" s="3">
+        <v>1100</v>
+      </c>
+      <c r="J81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K81" s="3">
         <v>800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>400</v>
       </c>
-      <c r="M81" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N81" s="3">
+      <c r="N81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O81" s="3">
         <v>500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>600</v>
-      </c>
-      <c r="Q81" s="3">
-        <v>400</v>
       </c>
       <c r="R81" s="3">
         <v>400</v>
       </c>
       <c r="S81" s="3">
+        <v>400</v>
+      </c>
+      <c r="T81" s="3">
         <v>500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>400</v>
       </c>
-      <c r="U81" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V81" s="3">
-        <v>0</v>
+      <c r="V81" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W81" s="3">
         <v>0</v>
@@ -7143,8 +7338,8 @@
       <c r="Z81" s="3">
         <v>0</v>
       </c>
-      <c r="AA81" s="3" t="s">
-        <v>4</v>
+      <c r="AA81" s="3">
+        <v>0</v>
       </c>
       <c r="AB81" s="3" t="s">
         <v>4</v>
@@ -7161,14 +7356,17 @@
       <c r="AF81" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AG81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH81" s="3">
         <v>-3100</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7203,8 +7401,9 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7301,8 +7500,11 @@
       <c r="AH83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7399,8 +7601,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7497,8 +7702,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7595,8 +7803,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7693,8 +7904,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7791,8 +8005,11 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -7889,8 +8106,11 @@
       <c r="AH89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7925,8 +8145,9 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8023,8 +8244,11 @@
       <c r="AH91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8121,8 +8345,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8219,8 +8446,11 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -8317,8 +8547,11 @@
       <c r="AH94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8353,8 +8586,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8451,8 +8685,11 @@
       <c r="AH96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8549,8 +8786,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8647,8 +8887,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8745,8 +8988,11 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8843,8 +9089,11 @@
       <c r="AH100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8941,8 +9190,11 @@
       <c r="AH101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -9037,6 +9289,9 @@
         <v>0</v>
       </c>
       <c r="AH102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ALBY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ALBY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="544" uniqueCount="92">
   <si>
     <t>ALBY</t>
   </si>
@@ -656,214 +656,218 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42916</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42825</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>39721</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>39629</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>2700</v>
+        <v>3000</v>
       </c>
       <c r="E8" s="3">
-        <v>2600</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>4</v>
+        <v>3000</v>
+      </c>
+      <c r="F8" s="3">
+        <v>2900</v>
       </c>
       <c r="G8" s="3">
-        <v>2600</v>
+        <v>2800</v>
       </c>
       <c r="H8" s="3">
-        <v>2700</v>
+        <v>2800</v>
       </c>
       <c r="I8" s="3">
-        <v>2700</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K8" s="3">
+        <v>3000</v>
+      </c>
+      <c r="J8" s="3">
+        <v>2900</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L8" s="3">
         <v>2400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1600</v>
       </c>
-      <c r="N8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O8" s="3">
+      <c r="O8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P8" s="3">
         <v>1800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1800</v>
-      </c>
-      <c r="R8" s="3">
-        <v>1700</v>
       </c>
       <c r="S8" s="3">
         <v>1700</v>
       </c>
       <c r="T8" s="3">
+        <v>1700</v>
+      </c>
+      <c r="U8" s="3">
         <v>1800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1700</v>
       </c>
-      <c r="V8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W8" s="3">
-        <v>0</v>
+      <c r="W8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X8" s="3">
         <v>0</v>
@@ -877,8 +881,8 @@
       <c r="AA8" s="3">
         <v>0</v>
       </c>
-      <c r="AB8" s="3" t="s">
-        <v>4</v>
+      <c r="AB8" s="3">
+        <v>0</v>
       </c>
       <c r="AC8" s="3" t="s">
         <v>4</v>
@@ -895,14 +899,17 @@
       <c r="AG8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AH8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI8" s="3">
         <v>2400</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>2600</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -1002,31 +1009,34 @@
       <c r="AI9" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ9" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>4</v>
+      <c r="D10" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E10" s="3">
+        <v>3000</v>
+      </c>
+      <c r="F10" s="3">
+        <v>2900</v>
+      </c>
+      <c r="G10" s="3">
+        <v>2800</v>
+      </c>
+      <c r="H10" s="3">
+        <v>2800</v>
+      </c>
+      <c r="I10" s="3">
+        <v>3000</v>
+      </c>
+      <c r="J10" s="3">
+        <v>2900</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>4</v>
@@ -1103,8 +1113,11 @@
       <c r="AI10" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ10" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1140,8 +1153,9 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1241,8 +1255,11 @@
       <c r="AI12" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1342,31 +1359,34 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1443,8 +1463,11 @@
       <c r="AI14" s="3">
         <v>0</v>
       </c>
+      <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1526,8 +1549,8 @@
       <c r="AC15" s="3">
         <v>0</v>
       </c>
-      <c r="AD15" s="3" t="s">
-        <v>4</v>
+      <c r="AD15" s="3">
+        <v>0</v>
       </c>
       <c r="AE15" s="3" t="s">
         <v>4</v>
@@ -1544,8 +1567,11 @@
       <c r="AI15" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ15" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1578,31 +1604,32 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="E17" s="3">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="F17" s="3">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="G17" s="3">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="H17" s="3">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="I17" s="3">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="J17" s="3">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="K17" s="3">
         <v>0</v>
@@ -1619,8 +1646,8 @@
       <c r="O17" s="3">
         <v>0</v>
       </c>
-      <c r="P17" s="3" t="s">
-        <v>4</v>
+      <c r="P17" s="3">
+        <v>0</v>
       </c>
       <c r="Q17" s="3" t="s">
         <v>4</v>
@@ -1637,8 +1664,8 @@
       <c r="U17" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V17" s="3">
-        <v>0</v>
+      <c r="V17" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W17" s="3">
         <v>0</v>
@@ -1655,8 +1682,8 @@
       <c r="AA17" s="3">
         <v>0</v>
       </c>
-      <c r="AB17" s="3" t="s">
-        <v>4</v>
+      <c r="AB17" s="3">
+        <v>0</v>
       </c>
       <c r="AC17" s="3" t="s">
         <v>4</v>
@@ -1673,56 +1700,59 @@
       <c r="AG17" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AH17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI17" s="3">
         <v>3700</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>2700</v>
+        <v>1500</v>
       </c>
       <c r="E18" s="3">
-        <v>2600</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>4</v>
+        <v>1500</v>
+      </c>
+      <c r="F18" s="3">
+        <v>1400</v>
       </c>
       <c r="G18" s="3">
-        <v>2600</v>
+        <v>1200</v>
       </c>
       <c r="H18" s="3">
-        <v>2700</v>
+        <v>1300</v>
       </c>
       <c r="I18" s="3">
-        <v>2700</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K18" s="3">
+        <v>1400</v>
+      </c>
+      <c r="J18" s="3">
+        <v>1400</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L18" s="3">
         <v>2400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1600</v>
       </c>
-      <c r="N18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O18" s="3">
+      <c r="O18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P18" s="3">
         <v>1800</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q18" s="3" t="s">
         <v>4</v>
       </c>
@@ -1741,8 +1771,8 @@
       <c r="V18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W18" s="3">
-        <v>0</v>
+      <c r="W18" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X18" s="3">
         <v>0</v>
@@ -1756,8 +1786,8 @@
       <c r="AA18" s="3">
         <v>0</v>
       </c>
-      <c r="AB18" s="3" t="s">
-        <v>4</v>
+      <c r="AB18" s="3">
+        <v>0</v>
       </c>
       <c r="AC18" s="3" t="s">
         <v>4</v>
@@ -1774,14 +1804,17 @@
       <c r="AG18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AH18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI18" s="3">
         <v>-1300</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1817,49 +1850,50 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="E20" s="3">
-        <v>-1300</v>
+      <c r="D20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G20" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="H20" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="I20" s="3">
-        <v>-1300</v>
+      <c r="G20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K20" s="3">
+      <c r="K20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L20" s="3">
         <v>-1400</v>
-      </c>
-      <c r="L20" s="3">
-        <v>-1100</v>
       </c>
       <c r="M20" s="3">
         <v>-1100</v>
       </c>
-      <c r="N20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O20" s="3">
+      <c r="N20" s="3">
         <v>-1100</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>4</v>
+      <c r="O20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P20" s="3">
+        <v>-1100</v>
       </c>
       <c r="Q20" s="3" t="s">
         <v>4</v>
@@ -1879,8 +1913,8 @@
       <c r="V20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W20" s="3">
-        <v>500</v>
+      <c r="W20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X20" s="3">
         <v>500</v>
@@ -1894,8 +1928,8 @@
       <c r="AA20" s="3">
         <v>500</v>
       </c>
-      <c r="AB20" s="3" t="s">
-        <v>4</v>
+      <c r="AB20" s="3">
+        <v>500</v>
       </c>
       <c r="AC20" s="3" t="s">
         <v>4</v>
@@ -1912,37 +1946,40 @@
       <c r="AG20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AH20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI20" s="3">
         <v>-3400</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-1700</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>4</v>
+      <c r="D21" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E21" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F21" s="3">
+        <v>1400</v>
+      </c>
+      <c r="G21" s="3">
+        <v>1200</v>
+      </c>
+      <c r="H21" s="3">
+        <v>1300</v>
+      </c>
+      <c r="I21" s="3">
+        <v>1400</v>
+      </c>
+      <c r="J21" s="3">
+        <v>1400</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>4</v>
@@ -2019,31 +2056,34 @@
       <c r="AI21" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ21" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -2120,8 +2160,11 @@
       <c r="AI22" s="3">
         <v>0</v>
       </c>
+      <c r="AJ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2129,16 +2172,16 @@
         <v>1500</v>
       </c>
       <c r="E23" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F23" s="3">
+        <v>1400</v>
+      </c>
+      <c r="G23" s="3">
+        <v>1200</v>
+      </c>
+      <c r="H23" s="3">
         <v>1300</v>
-      </c>
-      <c r="F23" s="3">
-        <v>1200</v>
-      </c>
-      <c r="G23" s="3">
-        <v>1300</v>
-      </c>
-      <c r="H23" s="3">
-        <v>1400</v>
       </c>
       <c r="I23" s="3">
         <v>1400</v>
@@ -2147,43 +2190,43 @@
         <v>1400</v>
       </c>
       <c r="K23" s="3">
+        <v>1400</v>
+      </c>
+      <c r="L23" s="3">
         <v>1000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>2500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>300</v>
-      </c>
-      <c r="W23" s="3">
-        <v>500</v>
       </c>
       <c r="X23" s="3">
         <v>500</v>
@@ -2198,31 +2241,34 @@
         <v>500</v>
       </c>
       <c r="AB23" s="3">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="AC23" s="3">
         <v>300</v>
       </c>
       <c r="AD23" s="3">
+        <v>300</v>
+      </c>
+      <c r="AE23" s="3">
         <v>400</v>
       </c>
-      <c r="AE23" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF23" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AG23" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AH23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI23" s="3">
         <v>-4700</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2230,46 +2276,46 @@
         <v>400</v>
       </c>
       <c r="E24" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="F24" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="G24" s="3">
         <v>300</v>
       </c>
       <c r="H24" s="3">
+        <v>300</v>
+      </c>
+      <c r="I24" s="3">
         <v>400</v>
-      </c>
-      <c r="I24" s="3">
-        <v>300</v>
       </c>
       <c r="J24" s="3">
         <v>300</v>
       </c>
       <c r="K24" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="L24" s="3">
         <v>200</v>
       </c>
       <c r="M24" s="3">
+        <v>200</v>
+      </c>
+      <c r="N24" s="3">
         <v>100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>600</v>
-      </c>
-      <c r="O24" s="3">
-        <v>100</v>
       </c>
       <c r="P24" s="3">
         <v>100</v>
       </c>
       <c r="Q24" s="3">
+        <v>100</v>
+      </c>
+      <c r="R24" s="3">
         <v>200</v>
-      </c>
-      <c r="R24" s="3">
-        <v>100</v>
       </c>
       <c r="S24" s="3">
         <v>100</v>
@@ -2305,25 +2351,28 @@
         <v>100</v>
       </c>
       <c r="AD24" s="3">
+        <v>100</v>
+      </c>
+      <c r="AE24" s="3">
         <v>2500</v>
       </c>
-      <c r="AE24" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF24" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AG24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AH24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI24" s="3">
         <v>-1600</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2423,8 +2472,11 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2432,61 +2484,61 @@
         <v>1100</v>
       </c>
       <c r="E26" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F26" s="3">
+        <v>1100</v>
+      </c>
+      <c r="G26" s="3">
+        <v>900</v>
+      </c>
+      <c r="H26" s="3">
         <v>1000</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G26" s="3">
-        <v>1000</v>
-      </c>
-      <c r="H26" s="3">
-        <v>1100</v>
       </c>
       <c r="I26" s="3">
         <v>1100</v>
       </c>
-      <c r="J26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K26" s="3">
+      <c r="J26" s="3">
+        <v>1100</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L26" s="3">
         <v>800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>400</v>
       </c>
-      <c r="N26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O26" s="3">
+      <c r="O26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P26" s="3">
         <v>500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>600</v>
-      </c>
-      <c r="R26" s="3">
-        <v>400</v>
       </c>
       <c r="S26" s="3">
         <v>400</v>
       </c>
       <c r="T26" s="3">
+        <v>400</v>
+      </c>
+      <c r="U26" s="3">
         <v>500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>400</v>
       </c>
-      <c r="V26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W26" s="3">
-        <v>0</v>
+      <c r="W26" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X26" s="3">
         <v>0</v>
@@ -2500,8 +2552,8 @@
       <c r="AA26" s="3">
         <v>0</v>
       </c>
-      <c r="AB26" s="3" t="s">
-        <v>4</v>
+      <c r="AB26" s="3">
+        <v>0</v>
       </c>
       <c r="AC26" s="3" t="s">
         <v>4</v>
@@ -2518,14 +2570,17 @@
       <c r="AG26" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AH26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI26" s="3">
         <v>-3100</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2533,61 +2588,61 @@
         <v>1100</v>
       </c>
       <c r="E27" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F27" s="3">
+        <v>1100</v>
+      </c>
+      <c r="G27" s="3">
+        <v>900</v>
+      </c>
+      <c r="H27" s="3">
         <v>1000</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G27" s="3">
-        <v>1000</v>
-      </c>
-      <c r="H27" s="3">
-        <v>1100</v>
       </c>
       <c r="I27" s="3">
         <v>1100</v>
       </c>
-      <c r="J27" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K27" s="3">
+      <c r="J27" s="3">
+        <v>1100</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L27" s="3">
         <v>800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>400</v>
       </c>
-      <c r="N27" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O27" s="3">
+      <c r="O27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P27" s="3">
         <v>500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>600</v>
-      </c>
-      <c r="R27" s="3">
-        <v>400</v>
       </c>
       <c r="S27" s="3">
         <v>400</v>
       </c>
       <c r="T27" s="3">
+        <v>400</v>
+      </c>
+      <c r="U27" s="3">
         <v>500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>400</v>
       </c>
-      <c r="V27" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W27" s="3">
-        <v>0</v>
+      <c r="W27" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X27" s="3">
         <v>0</v>
@@ -2601,8 +2656,8 @@
       <c r="AA27" s="3">
         <v>0</v>
       </c>
-      <c r="AB27" s="3" t="s">
-        <v>4</v>
+      <c r="AB27" s="3">
+        <v>0</v>
       </c>
       <c r="AC27" s="3" t="s">
         <v>4</v>
@@ -2619,14 +2674,17 @@
       <c r="AG27" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AH27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI27" s="3">
         <v>-3100</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2726,8 +2784,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2827,8 +2888,11 @@
       <c r="AI29" s="3">
         <v>0</v>
       </c>
+      <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2928,8 +2992,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3029,49 +3096,52 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>1200</v>
-      </c>
-      <c r="E32" s="3">
-        <v>1300</v>
+      <c r="D32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G32" s="3">
-        <v>1300</v>
-      </c>
-      <c r="H32" s="3">
-        <v>1300</v>
-      </c>
-      <c r="I32" s="3">
-        <v>1300</v>
+      <c r="G32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K32" s="3">
+      <c r="K32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L32" s="3">
         <v>1400</v>
-      </c>
-      <c r="L32" s="3">
-        <v>1100</v>
       </c>
       <c r="M32" s="3">
         <v>1100</v>
       </c>
-      <c r="N32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O32" s="3">
+      <c r="N32" s="3">
         <v>1100</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>4</v>
+      <c r="O32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P32" s="3">
+        <v>1100</v>
       </c>
       <c r="Q32" s="3" t="s">
         <v>4</v>
@@ -3091,8 +3161,8 @@
       <c r="V32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W32" s="3">
-        <v>-500</v>
+      <c r="W32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X32" s="3">
         <v>-500</v>
@@ -3106,8 +3176,8 @@
       <c r="AA32" s="3">
         <v>-500</v>
       </c>
-      <c r="AB32" s="3" t="s">
-        <v>4</v>
+      <c r="AB32" s="3">
+        <v>-500</v>
       </c>
       <c r="AC32" s="3" t="s">
         <v>4</v>
@@ -3124,14 +3194,17 @@
       <c r="AG32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AH32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI32" s="3">
         <v>3400</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3139,61 +3212,61 @@
         <v>1100</v>
       </c>
       <c r="E33" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F33" s="3">
+        <v>1100</v>
+      </c>
+      <c r="G33" s="3">
+        <v>900</v>
+      </c>
+      <c r="H33" s="3">
         <v>1000</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G33" s="3">
-        <v>1000</v>
-      </c>
-      <c r="H33" s="3">
-        <v>1100</v>
       </c>
       <c r="I33" s="3">
         <v>1100</v>
       </c>
-      <c r="J33" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K33" s="3">
+      <c r="J33" s="3">
+        <v>1100</v>
+      </c>
+      <c r="K33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L33" s="3">
         <v>800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>400</v>
       </c>
-      <c r="N33" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O33" s="3">
+      <c r="O33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P33" s="3">
         <v>500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>600</v>
-      </c>
-      <c r="R33" s="3">
-        <v>400</v>
       </c>
       <c r="S33" s="3">
         <v>400</v>
       </c>
       <c r="T33" s="3">
+        <v>400</v>
+      </c>
+      <c r="U33" s="3">
         <v>500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>400</v>
       </c>
-      <c r="V33" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W33" s="3">
-        <v>0</v>
+      <c r="W33" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X33" s="3">
         <v>0</v>
@@ -3207,8 +3280,8 @@
       <c r="AA33" s="3">
         <v>0</v>
       </c>
-      <c r="AB33" s="3" t="s">
-        <v>4</v>
+      <c r="AB33" s="3">
+        <v>0</v>
       </c>
       <c r="AC33" s="3" t="s">
         <v>4</v>
@@ -3225,14 +3298,17 @@
       <c r="AG33" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AH33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI33" s="3">
         <v>-3100</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3332,8 +3408,11 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3341,61 +3420,61 @@
         <v>1100</v>
       </c>
       <c r="E35" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F35" s="3">
+        <v>1100</v>
+      </c>
+      <c r="G35" s="3">
+        <v>900</v>
+      </c>
+      <c r="H35" s="3">
         <v>1000</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G35" s="3">
-        <v>1000</v>
-      </c>
-      <c r="H35" s="3">
-        <v>1100</v>
       </c>
       <c r="I35" s="3">
         <v>1100</v>
       </c>
-      <c r="J35" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K35" s="3">
+      <c r="J35" s="3">
+        <v>1100</v>
+      </c>
+      <c r="K35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L35" s="3">
         <v>800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>400</v>
       </c>
-      <c r="N35" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O35" s="3">
+      <c r="O35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P35" s="3">
         <v>500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>600</v>
-      </c>
-      <c r="R35" s="3">
-        <v>400</v>
       </c>
       <c r="S35" s="3">
         <v>400</v>
       </c>
       <c r="T35" s="3">
+        <v>400</v>
+      </c>
+      <c r="U35" s="3">
         <v>500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>400</v>
       </c>
-      <c r="V35" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W35" s="3">
-        <v>0</v>
+      <c r="W35" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X35" s="3">
         <v>0</v>
@@ -3409,8 +3488,8 @@
       <c r="AA35" s="3">
         <v>0</v>
       </c>
-      <c r="AB35" s="3" t="s">
-        <v>4</v>
+      <c r="AB35" s="3">
+        <v>0</v>
       </c>
       <c r="AC35" s="3" t="s">
         <v>4</v>
@@ -3427,120 +3506,126 @@
       <c r="AG35" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AH35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI35" s="3">
         <v>-3100</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42916</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42825</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>39721</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>39629</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3576,8 +3661,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3613,31 +3699,32 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D41" s="3">
-        <v>0</v>
-      </c>
-      <c r="E41" s="3">
-        <v>0</v>
-      </c>
-      <c r="F41" s="3">
-        <v>0</v>
-      </c>
-      <c r="G41" s="3">
-        <v>0</v>
-      </c>
-      <c r="H41" s="3">
-        <v>0</v>
-      </c>
-      <c r="I41" s="3">
-        <v>0</v>
-      </c>
-      <c r="J41" s="3">
-        <v>0</v>
+      <c r="D41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K41" s="3">
         <v>0</v>
@@ -3709,13 +3796,16 @@
         <v>0</v>
       </c>
       <c r="AH41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI41" s="3">
         <v>4100</v>
       </c>
-      <c r="AI41" s="3" t="s">
+      <c r="AJ41" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3810,36 +3900,39 @@
         <v>0</v>
       </c>
       <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI42" s="3">
         <v>900</v>
       </c>
-      <c r="AI42" s="3" t="s">
+      <c r="AJ42" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
-        <v>0</v>
-      </c>
-      <c r="E43" s="3">
-        <v>0</v>
-      </c>
-      <c r="F43" s="3">
-        <v>0</v>
-      </c>
-      <c r="G43" s="3">
-        <v>0</v>
-      </c>
-      <c r="H43" s="3">
-        <v>0</v>
-      </c>
-      <c r="I43" s="3">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3">
-        <v>0</v>
+      <c r="D43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
@@ -3916,31 +4009,34 @@
       <c r="AI43" s="3">
         <v>0</v>
       </c>
+      <c r="AJ43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -4017,31 +4113,34 @@
       <c r="AI44" s="3">
         <v>0</v>
       </c>
+      <c r="AJ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>0</v>
-      </c>
-      <c r="E45" s="3">
-        <v>0</v>
-      </c>
-      <c r="F45" s="3">
-        <v>0</v>
-      </c>
-      <c r="G45" s="3">
-        <v>0</v>
-      </c>
-      <c r="H45" s="3">
-        <v>0</v>
-      </c>
-      <c r="I45" s="3">
-        <v>0</v>
-      </c>
-      <c r="J45" s="3">
-        <v>0</v>
+      <c r="D45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K45" s="3">
         <v>0</v>
@@ -4118,31 +4217,34 @@
       <c r="AI45" s="3">
         <v>0</v>
       </c>
+      <c r="AJ45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D46" s="3">
-        <v>0</v>
-      </c>
-      <c r="E46" s="3">
-        <v>0</v>
-      </c>
-      <c r="F46" s="3">
-        <v>0</v>
-      </c>
-      <c r="G46" s="3">
-        <v>0</v>
-      </c>
-      <c r="H46" s="3">
-        <v>0</v>
-      </c>
-      <c r="I46" s="3">
-        <v>0</v>
-      </c>
-      <c r="J46" s="3">
-        <v>0</v>
+      <c r="D46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J46" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
@@ -4219,31 +4321,34 @@
       <c r="AI46" s="3">
         <v>0</v>
       </c>
+      <c r="AJ46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -4320,31 +4425,34 @@
       <c r="AI47" s="3">
         <v>0</v>
       </c>
+      <c r="AJ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
-        <v>0</v>
-      </c>
-      <c r="E48" s="3">
-        <v>0</v>
-      </c>
-      <c r="F48" s="3">
-        <v>0</v>
-      </c>
-      <c r="G48" s="3">
-        <v>0</v>
-      </c>
-      <c r="H48" s="3">
-        <v>0</v>
-      </c>
-      <c r="I48" s="3">
-        <v>0</v>
-      </c>
-      <c r="J48" s="3">
-        <v>0</v>
+      <c r="D48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K48" s="3">
         <v>0</v>
@@ -4416,13 +4524,16 @@
         <v>0</v>
       </c>
       <c r="AH48" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI48" s="3">
         <v>6400</v>
       </c>
-      <c r="AI48" s="3" t="s">
+      <c r="AJ48" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4517,13 +4628,16 @@
         <v>0</v>
       </c>
       <c r="AH49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI49" s="3">
         <v>2500</v>
       </c>
-      <c r="AI49" s="3" t="s">
+      <c r="AJ49" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4623,8 +4737,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4724,31 +4841,34 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>0</v>
-      </c>
-      <c r="E52" s="3">
-        <v>0</v>
-      </c>
-      <c r="F52" s="3">
-        <v>0</v>
-      </c>
-      <c r="G52" s="3">
-        <v>0</v>
-      </c>
-      <c r="H52" s="3">
-        <v>0</v>
-      </c>
-      <c r="I52" s="3">
-        <v>0</v>
-      </c>
-      <c r="J52" s="3">
-        <v>0</v>
+      <c r="D52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K52" s="3">
         <v>0</v>
@@ -4825,8 +4945,11 @@
       <c r="AI52" s="3">
         <v>0</v>
       </c>
+      <c r="AJ52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4926,31 +5049,34 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D54" s="3">
-        <v>0</v>
-      </c>
-      <c r="E54" s="3">
-        <v>0</v>
-      </c>
-      <c r="F54" s="3">
-        <v>0</v>
-      </c>
-      <c r="G54" s="3">
-        <v>0</v>
-      </c>
-      <c r="H54" s="3">
-        <v>0</v>
-      </c>
-      <c r="I54" s="3">
-        <v>0</v>
-      </c>
-      <c r="J54" s="3">
-        <v>0</v>
+      <c r="D54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J54" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K54" s="3">
         <v>0</v>
@@ -5022,13 +5148,16 @@
         <v>0</v>
       </c>
       <c r="AH54" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI54" s="3">
         <v>198900</v>
       </c>
-      <c r="AI54" s="3" t="s">
+      <c r="AJ54" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5064,8 +5193,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5101,31 +5231,32 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
-        <v>0</v>
-      </c>
-      <c r="E57" s="3">
-        <v>0</v>
-      </c>
-      <c r="F57" s="3">
-        <v>0</v>
-      </c>
-      <c r="G57" s="3">
-        <v>0</v>
-      </c>
-      <c r="H57" s="3">
-        <v>0</v>
-      </c>
-      <c r="I57" s="3">
-        <v>0</v>
-      </c>
-      <c r="J57" s="3">
-        <v>0</v>
+      <c r="D57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K57" s="3">
         <v>0</v>
@@ -5202,8 +5333,11 @@
       <c r="AI57" s="3">
         <v>0</v>
       </c>
+      <c r="AJ57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5303,31 +5437,34 @@
       <c r="AI58" s="3">
         <v>0</v>
       </c>
+      <c r="AJ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
-        <v>0</v>
-      </c>
-      <c r="E59" s="3">
-        <v>0</v>
-      </c>
-      <c r="F59" s="3">
-        <v>0</v>
-      </c>
-      <c r="G59" s="3">
-        <v>0</v>
-      </c>
-      <c r="H59" s="3">
-        <v>0</v>
-      </c>
-      <c r="I59" s="3">
-        <v>0</v>
-      </c>
-      <c r="J59" s="3">
-        <v>0</v>
+      <c r="D59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K59" s="3">
         <v>0</v>
@@ -5404,31 +5541,34 @@
       <c r="AI59" s="3">
         <v>0</v>
       </c>
+      <c r="AJ59" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="3">
-        <v>0</v>
-      </c>
-      <c r="E60" s="3">
-        <v>0</v>
-      </c>
-      <c r="F60" s="3">
-        <v>0</v>
-      </c>
-      <c r="G60" s="3">
-        <v>0</v>
-      </c>
-      <c r="H60" s="3">
-        <v>0</v>
-      </c>
-      <c r="I60" s="3">
-        <v>0</v>
-      </c>
-      <c r="J60" s="3">
-        <v>0</v>
+      <c r="D60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J60" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K60" s="3">
         <v>0</v>
@@ -5505,8 +5645,11 @@
       <c r="AI60" s="3">
         <v>0</v>
       </c>
+      <c r="AJ60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5606,31 +5749,34 @@
       <c r="AI61" s="3">
         <v>0</v>
       </c>
+      <c r="AJ61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>0</v>
-      </c>
-      <c r="E62" s="3">
-        <v>0</v>
-      </c>
-      <c r="F62" s="3">
-        <v>0</v>
-      </c>
-      <c r="G62" s="3">
-        <v>0</v>
-      </c>
-      <c r="H62" s="3">
-        <v>0</v>
-      </c>
-      <c r="I62" s="3">
-        <v>0</v>
-      </c>
-      <c r="J62" s="3">
-        <v>0</v>
+      <c r="D62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K62" s="3">
         <v>0</v>
@@ -5707,8 +5853,11 @@
       <c r="AI62" s="3">
         <v>0</v>
       </c>
+      <c r="AJ62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5808,8 +5957,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5909,8 +6061,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6010,31 +6165,34 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D66" s="3">
-        <v>0</v>
-      </c>
-      <c r="E66" s="3">
-        <v>0</v>
-      </c>
-      <c r="F66" s="3">
-        <v>0</v>
-      </c>
-      <c r="G66" s="3">
-        <v>0</v>
-      </c>
-      <c r="H66" s="3">
-        <v>0</v>
-      </c>
-      <c r="I66" s="3">
-        <v>0</v>
-      </c>
-      <c r="J66" s="3">
-        <v>0</v>
+      <c r="D66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J66" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K66" s="3">
         <v>0</v>
@@ -6106,13 +6264,16 @@
         <v>0</v>
       </c>
       <c r="AH66" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI66" s="3">
         <v>177800</v>
       </c>
-      <c r="AI66" s="3" t="s">
+      <c r="AJ66" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6148,8 +6309,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6249,8 +6411,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6350,8 +6515,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6451,8 +6619,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6552,31 +6723,34 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
-        <v>0</v>
-      </c>
-      <c r="E72" s="3">
-        <v>0</v>
-      </c>
-      <c r="F72" s="3">
-        <v>0</v>
-      </c>
-      <c r="G72" s="3">
-        <v>0</v>
-      </c>
-      <c r="H72" s="3">
-        <v>0</v>
-      </c>
-      <c r="I72" s="3">
-        <v>0</v>
-      </c>
-      <c r="J72" s="3">
-        <v>0</v>
+      <c r="D72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J72" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K72" s="3">
         <v>0</v>
@@ -6653,8 +6827,11 @@
       <c r="AI72" s="3">
         <v>0</v>
       </c>
+      <c r="AJ72" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6754,8 +6931,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6855,8 +7035,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6956,68 +7139,71 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D76" s="3">
-        <v>26100</v>
-      </c>
-      <c r="E76" s="3">
-        <v>25900</v>
-      </c>
-      <c r="F76" s="3">
-        <v>23200</v>
-      </c>
-      <c r="G76" s="3">
-        <v>23700</v>
-      </c>
-      <c r="H76" s="3">
-        <v>23600</v>
-      </c>
-      <c r="I76" s="3">
-        <v>22800</v>
-      </c>
-      <c r="J76" s="3">
+      <c r="D76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K76" s="3">
         <v>20800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>21000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>20500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>20400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>19100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>19600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>19100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>18600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>17000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>16800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>17100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>16600</v>
       </c>
-      <c r="V76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W76" s="3" t="s">
         <v>4</v>
       </c>
@@ -7030,8 +7216,8 @@
       <c r="Z76" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA76" s="3">
-        <v>0</v>
+      <c r="AA76" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AB76" s="3">
         <v>0</v>
@@ -7052,13 +7238,16 @@
         <v>0</v>
       </c>
       <c r="AH76" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI76" s="3">
         <v>21100</v>
       </c>
-      <c r="AI76" s="3" t="s">
+      <c r="AJ76" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7158,114 +7347,120 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42916</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42825</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>39721</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>39629</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -7273,61 +7468,61 @@
         <v>1100</v>
       </c>
       <c r="E81" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F81" s="3">
+        <v>1100</v>
+      </c>
+      <c r="G81" s="3">
+        <v>900</v>
+      </c>
+      <c r="H81" s="3">
         <v>1000</v>
-      </c>
-      <c r="F81" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G81" s="3">
-        <v>1000</v>
-      </c>
-      <c r="H81" s="3">
-        <v>1100</v>
       </c>
       <c r="I81" s="3">
         <v>1100</v>
       </c>
-      <c r="J81" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K81" s="3">
+      <c r="J81" s="3">
+        <v>1100</v>
+      </c>
+      <c r="K81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L81" s="3">
         <v>800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>400</v>
       </c>
-      <c r="N81" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O81" s="3">
+      <c r="O81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P81" s="3">
         <v>500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>600</v>
-      </c>
-      <c r="R81" s="3">
-        <v>400</v>
       </c>
       <c r="S81" s="3">
         <v>400</v>
       </c>
       <c r="T81" s="3">
+        <v>400</v>
+      </c>
+      <c r="U81" s="3">
         <v>500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>400</v>
       </c>
-      <c r="V81" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W81" s="3">
-        <v>0</v>
+      <c r="W81" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X81" s="3">
         <v>0</v>
@@ -7341,8 +7536,8 @@
       <c r="AA81" s="3">
         <v>0</v>
       </c>
-      <c r="AB81" s="3" t="s">
-        <v>4</v>
+      <c r="AB81" s="3">
+        <v>0</v>
       </c>
       <c r="AC81" s="3" t="s">
         <v>4</v>
@@ -7359,14 +7554,17 @@
       <c r="AG81" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AH81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI81" s="3">
         <v>-3100</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7402,31 +7600,32 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
-        <v>0</v>
-      </c>
-      <c r="E83" s="3">
-        <v>0</v>
-      </c>
-      <c r="F83" s="3">
-        <v>0</v>
-      </c>
-      <c r="G83" s="3">
-        <v>0</v>
-      </c>
-      <c r="H83" s="3">
-        <v>0</v>
-      </c>
-      <c r="I83" s="3">
-        <v>0</v>
-      </c>
-      <c r="J83" s="3">
-        <v>0</v>
+      <c r="D83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K83" s="3">
         <v>0</v>
@@ -7503,8 +7702,11 @@
       <c r="AI83" s="3">
         <v>0</v>
       </c>
+      <c r="AJ83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7604,8 +7806,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7705,8 +7910,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7806,8 +8014,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7907,8 +8118,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8008,31 +8222,34 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
-        <v>0</v>
-      </c>
-      <c r="E89" s="3">
-        <v>0</v>
-      </c>
-      <c r="F89" s="3">
-        <v>0</v>
-      </c>
-      <c r="G89" s="3">
-        <v>0</v>
-      </c>
-      <c r="H89" s="3">
-        <v>0</v>
-      </c>
-      <c r="I89" s="3">
-        <v>0</v>
-      </c>
-      <c r="J89" s="3">
-        <v>0</v>
+      <c r="D89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J89" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K89" s="3">
         <v>0</v>
@@ -8109,8 +8326,11 @@
       <c r="AI89" s="3">
         <v>0</v>
       </c>
+      <c r="AJ89" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8146,31 +8366,32 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
-      </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -8247,8 +8468,11 @@
       <c r="AI91" s="3">
         <v>0</v>
       </c>
+      <c r="AJ91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8348,8 +8572,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8449,31 +8676,34 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>0</v>
-      </c>
-      <c r="E94" s="3">
-        <v>0</v>
-      </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
-      <c r="J94" s="3">
-        <v>0</v>
+      <c r="D94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K94" s="3">
         <v>0</v>
@@ -8550,8 +8780,11 @@
       <c r="AI94" s="3">
         <v>0</v>
       </c>
+      <c r="AJ94" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8587,31 +8820,32 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -8688,8 +8922,11 @@
       <c r="AI96" s="3">
         <v>0</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8789,8 +9026,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8890,8 +9130,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8991,31 +9234,34 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
-        <v>0</v>
-      </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
-      <c r="J100" s="3">
-        <v>0</v>
+      <c r="D100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K100" s="3">
         <v>0</v>
@@ -9092,31 +9338,34 @@
       <c r="AI100" s="3">
         <v>0</v>
       </c>
+      <c r="AJ100" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -9193,31 +9442,34 @@
       <c r="AI101" s="3">
         <v>0</v>
       </c>
+      <c r="AJ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3">
-        <v>0</v>
-      </c>
-      <c r="E102" s="3">
-        <v>0</v>
-      </c>
-      <c r="F102" s="3">
-        <v>0</v>
-      </c>
-      <c r="G102" s="3">
-        <v>0</v>
-      </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
-      <c r="J102" s="3">
-        <v>0</v>
+      <c r="D102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J102" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K102" s="3">
         <v>0</v>
@@ -9292,6 +9544,9 @@
         <v>0</v>
       </c>
       <c r="AI102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ALBY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ALBY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="544" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="574" uniqueCount="92">
   <si>
     <t>ALBY</t>
   </si>
@@ -656,221 +656,224 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42916</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42825</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>39721</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>39629</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>3000</v>
+        <v>3100</v>
       </c>
       <c r="E8" s="3">
         <v>3000</v>
       </c>
       <c r="F8" s="3">
+        <v>3000</v>
+      </c>
+      <c r="G8" s="3">
         <v>2900</v>
-      </c>
-      <c r="G8" s="3">
-        <v>2800</v>
       </c>
       <c r="H8" s="3">
         <v>2800</v>
       </c>
       <c r="I8" s="3">
+        <v>2800</v>
+      </c>
+      <c r="J8" s="3">
         <v>3000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2900</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L8" s="3">
+      <c r="L8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M8" s="3">
         <v>2400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1600</v>
       </c>
-      <c r="O8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P8" s="3">
+      <c r="P8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q8" s="3">
         <v>1800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1800</v>
-      </c>
-      <c r="S8" s="3">
-        <v>1700</v>
       </c>
       <c r="T8" s="3">
         <v>1700</v>
       </c>
       <c r="U8" s="3">
+        <v>1700</v>
+      </c>
+      <c r="V8" s="3">
         <v>1800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1700</v>
       </c>
-      <c r="W8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X8" s="3">
-        <v>0</v>
+      <c r="X8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Y8" s="3">
         <v>0</v>
@@ -884,8 +887,8 @@
       <c r="AB8" s="3">
         <v>0</v>
       </c>
-      <c r="AC8" s="3" t="s">
-        <v>4</v>
+      <c r="AC8" s="3">
+        <v>0</v>
       </c>
       <c r="AD8" s="3" t="s">
         <v>4</v>
@@ -902,14 +905,17 @@
       <c r="AH8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AI8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ8" s="3">
         <v>2400</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>2600</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -1012,35 +1018,38 @@
       <c r="AJ9" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK9" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>3000</v>
+        <v>3100</v>
       </c>
       <c r="E10" s="3">
         <v>3000</v>
       </c>
       <c r="F10" s="3">
+        <v>3000</v>
+      </c>
+      <c r="G10" s="3">
         <v>2900</v>
-      </c>
-      <c r="G10" s="3">
-        <v>2800</v>
       </c>
       <c r="H10" s="3">
         <v>2800</v>
       </c>
       <c r="I10" s="3">
+        <v>2800</v>
+      </c>
+      <c r="J10" s="3">
         <v>3000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2900</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>4</v>
       </c>
@@ -1116,8 +1125,11 @@
       <c r="AJ10" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK10" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1154,8 +1166,9 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1258,8 +1271,11 @@
       <c r="AJ12" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK12" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1362,8 +1378,11 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1388,8 +1407,8 @@
       <c r="J14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -1466,8 +1485,11 @@
       <c r="AJ14" s="3">
         <v>0</v>
       </c>
+      <c r="AK14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1552,8 +1574,8 @@
       <c r="AD15" s="3">
         <v>0</v>
       </c>
-      <c r="AE15" s="3" t="s">
-        <v>4</v>
+      <c r="AE15" s="3">
+        <v>0</v>
       </c>
       <c r="AF15" s="3" t="s">
         <v>4</v>
@@ -1570,8 +1592,11 @@
       <c r="AJ15" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK15" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1605,13 +1630,14 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1500</v>
+        <v>1700</v>
       </c>
       <c r="E17" s="3">
         <v>1500</v>
@@ -1620,10 +1646,10 @@
         <v>1500</v>
       </c>
       <c r="G17" s="3">
+        <v>1500</v>
+      </c>
+      <c r="H17" s="3">
         <v>1600</v>
-      </c>
-      <c r="H17" s="3">
-        <v>1500</v>
       </c>
       <c r="I17" s="3">
         <v>1500</v>
@@ -1632,7 +1658,7 @@
         <v>1500</v>
       </c>
       <c r="K17" s="3">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="L17" s="3">
         <v>0</v>
@@ -1649,8 +1675,8 @@
       <c r="P17" s="3">
         <v>0</v>
       </c>
-      <c r="Q17" s="3" t="s">
-        <v>4</v>
+      <c r="Q17" s="3">
+        <v>0</v>
       </c>
       <c r="R17" s="3" t="s">
         <v>4</v>
@@ -1667,8 +1693,8 @@
       <c r="V17" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W17" s="3">
-        <v>0</v>
+      <c r="W17" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X17" s="3">
         <v>0</v>
@@ -1685,8 +1711,8 @@
       <c r="AB17" s="3">
         <v>0</v>
       </c>
-      <c r="AC17" s="3" t="s">
-        <v>4</v>
+      <c r="AC17" s="3">
+        <v>0</v>
       </c>
       <c r="AD17" s="3" t="s">
         <v>4</v>
@@ -1703,59 +1729,62 @@
       <c r="AH17" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AI17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ17" s="3">
         <v>3700</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>1500</v>
+        <v>1400</v>
       </c>
       <c r="E18" s="3">
         <v>1500</v>
       </c>
       <c r="F18" s="3">
+        <v>1500</v>
+      </c>
+      <c r="G18" s="3">
         <v>1400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1300</v>
-      </c>
-      <c r="I18" s="3">
-        <v>1400</v>
       </c>
       <c r="J18" s="3">
         <v>1400</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L18" s="3">
+      <c r="K18" s="3">
+        <v>1400</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M18" s="3">
         <v>2400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1600</v>
       </c>
-      <c r="O18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P18" s="3">
+      <c r="P18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q18" s="3">
         <v>1800</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R18" s="3" t="s">
         <v>4</v>
       </c>
@@ -1774,8 +1803,8 @@
       <c r="W18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X18" s="3">
-        <v>0</v>
+      <c r="X18" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Y18" s="3">
         <v>0</v>
@@ -1789,8 +1818,8 @@
       <c r="AB18" s="3">
         <v>0</v>
       </c>
-      <c r="AC18" s="3" t="s">
-        <v>4</v>
+      <c r="AC18" s="3">
+        <v>0</v>
       </c>
       <c r="AD18" s="3" t="s">
         <v>4</v>
@@ -1807,14 +1836,17 @@
       <c r="AH18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AI18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ18" s="3">
         <v>-1300</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1851,8 +1883,9 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1880,23 +1913,23 @@
       <c r="K20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L20" s="3">
+      <c r="L20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M20" s="3">
         <v>-1400</v>
-      </c>
-      <c r="M20" s="3">
-        <v>-1100</v>
       </c>
       <c r="N20" s="3">
         <v>-1100</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P20" s="3">
+      <c r="O20" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q20" s="3" t="s">
-        <v>4</v>
+      <c r="P20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>-1100</v>
       </c>
       <c r="R20" s="3" t="s">
         <v>4</v>
@@ -1916,8 +1949,8 @@
       <c r="W20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X20" s="3">
-        <v>500</v>
+      <c r="X20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Y20" s="3">
         <v>500</v>
@@ -1931,8 +1964,8 @@
       <c r="AB20" s="3">
         <v>500</v>
       </c>
-      <c r="AC20" s="3" t="s">
-        <v>4</v>
+      <c r="AC20" s="3">
+        <v>500</v>
       </c>
       <c r="AD20" s="3" t="s">
         <v>4</v>
@@ -1949,40 +1982,43 @@
       <c r="AH20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AI20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ20" s="3">
         <v>-3400</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-1700</v>
       </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1500</v>
+        <v>1400</v>
       </c>
       <c r="E21" s="3">
         <v>1500</v>
       </c>
       <c r="F21" s="3">
+        <v>1500</v>
+      </c>
+      <c r="G21" s="3">
         <v>1400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1300</v>
-      </c>
-      <c r="I21" s="3">
-        <v>1400</v>
       </c>
       <c r="J21" s="3">
         <v>1400</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>4</v>
+      <c r="K21" s="3">
+        <v>1400</v>
       </c>
       <c r="L21" s="3" t="s">
         <v>4</v>
@@ -2059,8 +2095,11 @@
       <c r="AJ21" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK21" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2085,8 +2124,8 @@
       <c r="J22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -2163,28 +2202,31 @@
       <c r="AJ22" s="3">
         <v>0</v>
       </c>
+      <c r="AK22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>1500</v>
+        <v>1400</v>
       </c>
       <c r="E23" s="3">
         <v>1500</v>
       </c>
       <c r="F23" s="3">
+        <v>1500</v>
+      </c>
+      <c r="G23" s="3">
         <v>1400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1300</v>
-      </c>
-      <c r="I23" s="3">
-        <v>1400</v>
       </c>
       <c r="J23" s="3">
         <v>1400</v>
@@ -2193,43 +2235,43 @@
         <v>1400</v>
       </c>
       <c r="L23" s="3">
+        <v>1400</v>
+      </c>
+      <c r="M23" s="3">
         <v>1000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>2500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>300</v>
-      </c>
-      <c r="X23" s="3">
-        <v>500</v>
       </c>
       <c r="Y23" s="3">
         <v>500</v>
@@ -2244,36 +2286,39 @@
         <v>500</v>
       </c>
       <c r="AC23" s="3">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="AD23" s="3">
         <v>300</v>
       </c>
       <c r="AE23" s="3">
+        <v>300</v>
+      </c>
+      <c r="AF23" s="3">
         <v>400</v>
       </c>
-      <c r="AF23" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AG23" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AH23" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AI23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ23" s="3">
         <v>-4700</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="E24" s="3">
         <v>400</v>
@@ -2282,43 +2327,43 @@
         <v>400</v>
       </c>
       <c r="G24" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="H24" s="3">
         <v>300</v>
       </c>
       <c r="I24" s="3">
+        <v>300</v>
+      </c>
+      <c r="J24" s="3">
         <v>400</v>
-      </c>
-      <c r="J24" s="3">
-        <v>300</v>
       </c>
       <c r="K24" s="3">
         <v>300</v>
       </c>
       <c r="L24" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="M24" s="3">
         <v>200</v>
       </c>
       <c r="N24" s="3">
+        <v>200</v>
+      </c>
+      <c r="O24" s="3">
         <v>100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>600</v>
-      </c>
-      <c r="P24" s="3">
-        <v>100</v>
       </c>
       <c r="Q24" s="3">
         <v>100</v>
       </c>
       <c r="R24" s="3">
+        <v>100</v>
+      </c>
+      <c r="S24" s="3">
         <v>200</v>
-      </c>
-      <c r="S24" s="3">
-        <v>100</v>
       </c>
       <c r="T24" s="3">
         <v>100</v>
@@ -2354,25 +2399,28 @@
         <v>100</v>
       </c>
       <c r="AE24" s="3">
+        <v>100</v>
+      </c>
+      <c r="AF24" s="3">
         <v>2500</v>
       </c>
-      <c r="AF24" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AG24" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AH24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AI24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ24" s="3">
         <v>-1600</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2475,13 +2523,16 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="E26" s="3">
         <v>1100</v>
@@ -2490,58 +2541,58 @@
         <v>1100</v>
       </c>
       <c r="G26" s="3">
+        <v>1100</v>
+      </c>
+      <c r="H26" s="3">
         <v>900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1000</v>
-      </c>
-      <c r="I26" s="3">
-        <v>1100</v>
       </c>
       <c r="J26" s="3">
         <v>1100</v>
       </c>
-      <c r="K26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L26" s="3">
+      <c r="K26" s="3">
+        <v>1100</v>
+      </c>
+      <c r="L26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M26" s="3">
         <v>800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>400</v>
       </c>
-      <c r="O26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P26" s="3">
+      <c r="P26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q26" s="3">
         <v>500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>600</v>
-      </c>
-      <c r="S26" s="3">
-        <v>400</v>
       </c>
       <c r="T26" s="3">
         <v>400</v>
       </c>
       <c r="U26" s="3">
+        <v>400</v>
+      </c>
+      <c r="V26" s="3">
         <v>500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>400</v>
       </c>
-      <c r="W26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X26" s="3">
-        <v>0</v>
+      <c r="X26" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Y26" s="3">
         <v>0</v>
@@ -2555,8 +2606,8 @@
       <c r="AB26" s="3">
         <v>0</v>
       </c>
-      <c r="AC26" s="3" t="s">
-        <v>4</v>
+      <c r="AC26" s="3">
+        <v>0</v>
       </c>
       <c r="AD26" s="3" t="s">
         <v>4</v>
@@ -2573,19 +2624,22 @@
       <c r="AH26" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AI26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ26" s="3">
         <v>-3100</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="E27" s="3">
         <v>1100</v>
@@ -2594,58 +2648,58 @@
         <v>1100</v>
       </c>
       <c r="G27" s="3">
+        <v>1100</v>
+      </c>
+      <c r="H27" s="3">
         <v>900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1000</v>
-      </c>
-      <c r="I27" s="3">
-        <v>1100</v>
       </c>
       <c r="J27" s="3">
         <v>1100</v>
       </c>
-      <c r="K27" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L27" s="3">
+      <c r="K27" s="3">
+        <v>1100</v>
+      </c>
+      <c r="L27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M27" s="3">
         <v>800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>400</v>
       </c>
-      <c r="O27" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P27" s="3">
+      <c r="P27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q27" s="3">
         <v>500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>600</v>
-      </c>
-      <c r="S27" s="3">
-        <v>400</v>
       </c>
       <c r="T27" s="3">
         <v>400</v>
       </c>
       <c r="U27" s="3">
+        <v>400</v>
+      </c>
+      <c r="V27" s="3">
         <v>500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>400</v>
       </c>
-      <c r="W27" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X27" s="3">
-        <v>0</v>
+      <c r="X27" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Y27" s="3">
         <v>0</v>
@@ -2659,8 +2713,8 @@
       <c r="AB27" s="3">
         <v>0</v>
       </c>
-      <c r="AC27" s="3" t="s">
-        <v>4</v>
+      <c r="AC27" s="3">
+        <v>0</v>
       </c>
       <c r="AD27" s="3" t="s">
         <v>4</v>
@@ -2677,14 +2731,17 @@
       <c r="AH27" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AI27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ27" s="3">
         <v>-3100</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2787,8 +2844,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2891,8 +2951,11 @@
       <c r="AJ29" s="3">
         <v>0</v>
       </c>
+      <c r="AK29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2995,8 +3058,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3099,8 +3165,11 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3128,23 +3197,23 @@
       <c r="K32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L32" s="3">
+      <c r="L32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M32" s="3">
         <v>1400</v>
-      </c>
-      <c r="M32" s="3">
-        <v>1100</v>
       </c>
       <c r="N32" s="3">
         <v>1100</v>
       </c>
-      <c r="O32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P32" s="3">
+      <c r="O32" s="3">
         <v>1100</v>
       </c>
-      <c r="Q32" s="3" t="s">
-        <v>4</v>
+      <c r="P32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>1100</v>
       </c>
       <c r="R32" s="3" t="s">
         <v>4</v>
@@ -3164,8 +3233,8 @@
       <c r="W32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X32" s="3">
-        <v>-500</v>
+      <c r="X32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Y32" s="3">
         <v>-500</v>
@@ -3179,8 +3248,8 @@
       <c r="AB32" s="3">
         <v>-500</v>
       </c>
-      <c r="AC32" s="3" t="s">
-        <v>4</v>
+      <c r="AC32" s="3">
+        <v>-500</v>
       </c>
       <c r="AD32" s="3" t="s">
         <v>4</v>
@@ -3197,19 +3266,22 @@
       <c r="AH32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AI32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ32" s="3">
         <v>3400</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="E33" s="3">
         <v>1100</v>
@@ -3218,58 +3290,58 @@
         <v>1100</v>
       </c>
       <c r="G33" s="3">
+        <v>1100</v>
+      </c>
+      <c r="H33" s="3">
         <v>900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1000</v>
-      </c>
-      <c r="I33" s="3">
-        <v>1100</v>
       </c>
       <c r="J33" s="3">
         <v>1100</v>
       </c>
-      <c r="K33" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L33" s="3">
+      <c r="K33" s="3">
+        <v>1100</v>
+      </c>
+      <c r="L33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M33" s="3">
         <v>800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>400</v>
       </c>
-      <c r="O33" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P33" s="3">
+      <c r="P33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q33" s="3">
         <v>500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>600</v>
-      </c>
-      <c r="S33" s="3">
-        <v>400</v>
       </c>
       <c r="T33" s="3">
         <v>400</v>
       </c>
       <c r="U33" s="3">
+        <v>400</v>
+      </c>
+      <c r="V33" s="3">
         <v>500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>400</v>
       </c>
-      <c r="W33" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X33" s="3">
-        <v>0</v>
+      <c r="X33" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Y33" s="3">
         <v>0</v>
@@ -3283,8 +3355,8 @@
       <c r="AB33" s="3">
         <v>0</v>
       </c>
-      <c r="AC33" s="3" t="s">
-        <v>4</v>
+      <c r="AC33" s="3">
+        <v>0</v>
       </c>
       <c r="AD33" s="3" t="s">
         <v>4</v>
@@ -3301,14 +3373,17 @@
       <c r="AH33" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AI33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ33" s="3">
         <v>-3100</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3411,13 +3486,16 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="E35" s="3">
         <v>1100</v>
@@ -3426,58 +3504,58 @@
         <v>1100</v>
       </c>
       <c r="G35" s="3">
+        <v>1100</v>
+      </c>
+      <c r="H35" s="3">
         <v>900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1000</v>
-      </c>
-      <c r="I35" s="3">
-        <v>1100</v>
       </c>
       <c r="J35" s="3">
         <v>1100</v>
       </c>
-      <c r="K35" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L35" s="3">
+      <c r="K35" s="3">
+        <v>1100</v>
+      </c>
+      <c r="L35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M35" s="3">
         <v>800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>400</v>
       </c>
-      <c r="O35" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P35" s="3">
+      <c r="P35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q35" s="3">
         <v>500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>600</v>
-      </c>
-      <c r="S35" s="3">
-        <v>400</v>
       </c>
       <c r="T35" s="3">
         <v>400</v>
       </c>
       <c r="U35" s="3">
+        <v>400</v>
+      </c>
+      <c r="V35" s="3">
         <v>500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>400</v>
       </c>
-      <c r="W35" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X35" s="3">
-        <v>0</v>
+      <c r="X35" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Y35" s="3">
         <v>0</v>
@@ -3491,8 +3569,8 @@
       <c r="AB35" s="3">
         <v>0</v>
       </c>
-      <c r="AC35" s="3" t="s">
-        <v>4</v>
+      <c r="AC35" s="3">
+        <v>0</v>
       </c>
       <c r="AD35" s="3" t="s">
         <v>4</v>
@@ -3509,123 +3587,129 @@
       <c r="AH35" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AI35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ35" s="3">
         <v>-3100</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42916</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42825</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>39721</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>39629</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3662,8 +3746,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3700,8 +3785,9 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -3726,8 +3812,8 @@
       <c r="J41" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K41" s="3">
-        <v>0</v>
+      <c r="K41" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L41" s="3">
         <v>0</v>
@@ -3799,13 +3885,16 @@
         <v>0</v>
       </c>
       <c r="AI41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ41" s="3">
         <v>4100</v>
       </c>
-      <c r="AJ41" s="3" t="s">
+      <c r="AK41" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3903,13 +3992,16 @@
         <v>0</v>
       </c>
       <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ42" s="3">
         <v>900</v>
       </c>
-      <c r="AJ42" s="3" t="s">
+      <c r="AK42" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3934,8 +4026,8 @@
       <c r="J43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
+      <c r="K43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L43" s="3">
         <v>0</v>
@@ -4012,8 +4104,11 @@
       <c r="AJ43" s="3">
         <v>0</v>
       </c>
+      <c r="AK43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4038,8 +4133,8 @@
       <c r="J44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -4116,8 +4211,11 @@
       <c r="AJ44" s="3">
         <v>0</v>
       </c>
+      <c r="AK44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4142,8 +4240,8 @@
       <c r="J45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K45" s="3">
-        <v>0</v>
+      <c r="K45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L45" s="3">
         <v>0</v>
@@ -4220,8 +4318,11 @@
       <c r="AJ45" s="3">
         <v>0</v>
       </c>
+      <c r="AK45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -4246,8 +4347,8 @@
       <c r="J46" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K46" s="3">
-        <v>0</v>
+      <c r="K46" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L46" s="3">
         <v>0</v>
@@ -4324,8 +4425,11 @@
       <c r="AJ46" s="3">
         <v>0</v>
       </c>
+      <c r="AK46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4350,8 +4454,8 @@
       <c r="J47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -4428,8 +4532,11 @@
       <c r="AJ47" s="3">
         <v>0</v>
       </c>
+      <c r="AK47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4454,8 +4561,8 @@
       <c r="J48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K48" s="3">
-        <v>0</v>
+      <c r="K48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L48" s="3">
         <v>0</v>
@@ -4527,13 +4634,16 @@
         <v>0</v>
       </c>
       <c r="AI48" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ48" s="3">
         <v>6400</v>
       </c>
-      <c r="AJ48" s="3" t="s">
+      <c r="AK48" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4631,13 +4741,16 @@
         <v>0</v>
       </c>
       <c r="AI49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ49" s="3">
         <v>2500</v>
       </c>
-      <c r="AJ49" s="3" t="s">
+      <c r="AK49" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4740,8 +4853,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4844,8 +4960,11 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4870,8 +4989,8 @@
       <c r="J52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K52" s="3">
-        <v>0</v>
+      <c r="K52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L52" s="3">
         <v>0</v>
@@ -4948,8 +5067,11 @@
       <c r="AJ52" s="3">
         <v>0</v>
       </c>
+      <c r="AK52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5052,8 +5174,11 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
@@ -5078,8 +5203,8 @@
       <c r="J54" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K54" s="3">
-        <v>0</v>
+      <c r="K54" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L54" s="3">
         <v>0</v>
@@ -5151,13 +5276,16 @@
         <v>0</v>
       </c>
       <c r="AI54" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ54" s="3">
         <v>198900</v>
       </c>
-      <c r="AJ54" s="3" t="s">
+      <c r="AK54" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5194,8 +5322,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5232,8 +5361,9 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -5258,8 +5388,8 @@
       <c r="J57" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K57" s="3">
-        <v>0</v>
+      <c r="K57" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L57" s="3">
         <v>0</v>
@@ -5336,8 +5466,11 @@
       <c r="AJ57" s="3">
         <v>0</v>
       </c>
+      <c r="AK57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5440,8 +5573,11 @@
       <c r="AJ58" s="3">
         <v>0</v>
       </c>
+      <c r="AK58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5466,8 +5602,8 @@
       <c r="J59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K59" s="3">
-        <v>0</v>
+      <c r="K59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L59" s="3">
         <v>0</v>
@@ -5544,8 +5680,11 @@
       <c r="AJ59" s="3">
         <v>0</v>
       </c>
+      <c r="AK59" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5570,8 +5709,8 @@
       <c r="J60" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K60" s="3">
-        <v>0</v>
+      <c r="K60" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L60" s="3">
         <v>0</v>
@@ -5648,8 +5787,11 @@
       <c r="AJ60" s="3">
         <v>0</v>
       </c>
+      <c r="AK60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5752,8 +5894,11 @@
       <c r="AJ61" s="3">
         <v>0</v>
       </c>
+      <c r="AK61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5778,8 +5923,8 @@
       <c r="J62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K62" s="3">
-        <v>0</v>
+      <c r="K62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L62" s="3">
         <v>0</v>
@@ -5856,8 +6001,11 @@
       <c r="AJ62" s="3">
         <v>0</v>
       </c>
+      <c r="AK62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5960,8 +6108,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6064,8 +6215,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6168,8 +6322,11 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
@@ -6194,8 +6351,8 @@
       <c r="J66" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K66" s="3">
-        <v>0</v>
+      <c r="K66" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L66" s="3">
         <v>0</v>
@@ -6267,13 +6424,16 @@
         <v>0</v>
       </c>
       <c r="AI66" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ66" s="3">
         <v>177800</v>
       </c>
-      <c r="AJ66" s="3" t="s">
+      <c r="AK66" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6310,8 +6470,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6414,8 +6575,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6518,8 +6682,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6622,8 +6789,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6726,8 +6896,11 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -6752,8 +6925,8 @@
       <c r="J72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K72" s="3">
-        <v>0</v>
+      <c r="K72" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L72" s="3">
         <v>0</v>
@@ -6830,8 +7003,11 @@
       <c r="AJ72" s="3">
         <v>0</v>
       </c>
+      <c r="AK72" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6934,8 +7110,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7038,8 +7217,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7142,8 +7324,11 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
@@ -7168,45 +7353,45 @@
       <c r="J76" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K76" s="3">
+      <c r="K76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L76" s="3">
         <v>20800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>21000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>20500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>20400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>19100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>19600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>19100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>18600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>17000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>16800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>17100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>16600</v>
       </c>
-      <c r="W76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X76" s="3" t="s">
         <v>4</v>
       </c>
@@ -7219,8 +7404,8 @@
       <c r="AA76" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB76" s="3">
-        <v>0</v>
+      <c r="AB76" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AC76" s="3">
         <v>0</v>
@@ -7241,13 +7426,16 @@
         <v>0</v>
       </c>
       <c r="AI76" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ76" s="3">
         <v>21100</v>
       </c>
-      <c r="AJ76" s="3" t="s">
+      <c r="AK76" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7350,122 +7538,128 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42916</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42825</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>39721</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>39629</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="E81" s="3">
         <v>1100</v>
@@ -7474,58 +7668,58 @@
         <v>1100</v>
       </c>
       <c r="G81" s="3">
+        <v>1100</v>
+      </c>
+      <c r="H81" s="3">
         <v>900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1000</v>
-      </c>
-      <c r="I81" s="3">
-        <v>1100</v>
       </c>
       <c r="J81" s="3">
         <v>1100</v>
       </c>
-      <c r="K81" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L81" s="3">
+      <c r="K81" s="3">
+        <v>1100</v>
+      </c>
+      <c r="L81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M81" s="3">
         <v>800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>400</v>
       </c>
-      <c r="O81" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P81" s="3">
+      <c r="P81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q81" s="3">
         <v>500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>600</v>
-      </c>
-      <c r="S81" s="3">
-        <v>400</v>
       </c>
       <c r="T81" s="3">
         <v>400</v>
       </c>
       <c r="U81" s="3">
+        <v>400</v>
+      </c>
+      <c r="V81" s="3">
         <v>500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>400</v>
       </c>
-      <c r="W81" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X81" s="3">
-        <v>0</v>
+      <c r="X81" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Y81" s="3">
         <v>0</v>
@@ -7539,8 +7733,8 @@
       <c r="AB81" s="3">
         <v>0</v>
       </c>
-      <c r="AC81" s="3" t="s">
-        <v>4</v>
+      <c r="AC81" s="3">
+        <v>0</v>
       </c>
       <c r="AD81" s="3" t="s">
         <v>4</v>
@@ -7557,14 +7751,17 @@
       <c r="AH81" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AI81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ81" s="3">
         <v>-3100</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7601,8 +7798,9 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7627,8 +7825,8 @@
       <c r="J83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K83" s="3">
-        <v>0</v>
+      <c r="K83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L83" s="3">
         <v>0</v>
@@ -7705,8 +7903,11 @@
       <c r="AJ83" s="3">
         <v>0</v>
       </c>
+      <c r="AK83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7809,8 +8010,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7913,8 +8117,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8017,8 +8224,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8121,8 +8331,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8225,8 +8438,11 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -8251,8 +8467,8 @@
       <c r="J89" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K89" s="3">
-        <v>0</v>
+      <c r="K89" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L89" s="3">
         <v>0</v>
@@ -8329,8 +8545,11 @@
       <c r="AJ89" s="3">
         <v>0</v>
       </c>
+      <c r="AK89" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8367,8 +8586,9 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8393,8 +8613,8 @@
       <c r="J91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
+      <c r="K91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L91" s="3">
         <v>0</v>
@@ -8471,8 +8691,11 @@
       <c r="AJ91" s="3">
         <v>0</v>
       </c>
+      <c r="AK91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8575,8 +8798,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8679,8 +8905,11 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -8705,8 +8934,8 @@
       <c r="J94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
+      <c r="K94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L94" s="3">
         <v>0</v>
@@ -8783,8 +9012,11 @@
       <c r="AJ94" s="3">
         <v>0</v>
       </c>
+      <c r="AK94" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8821,8 +9053,9 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8847,8 +9080,8 @@
       <c r="J96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -8925,8 +9158,11 @@
       <c r="AJ96" s="3">
         <v>0</v>
       </c>
+      <c r="AK96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9029,8 +9265,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9133,8 +9372,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9237,8 +9479,11 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -9263,8 +9508,8 @@
       <c r="J100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
+      <c r="K100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L100" s="3">
         <v>0</v>
@@ -9341,8 +9586,11 @@
       <c r="AJ100" s="3">
         <v>0</v>
       </c>
+      <c r="AK100" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9367,8 +9615,8 @@
       <c r="J101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -9445,8 +9693,11 @@
       <c r="AJ101" s="3">
         <v>0</v>
       </c>
+      <c r="AK101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -9471,8 +9722,8 @@
       <c r="J102" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K102" s="3">
-        <v>0</v>
+      <c r="K102" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L102" s="3">
         <v>0</v>
@@ -9547,6 +9798,9 @@
         <v>0</v>
       </c>
       <c r="AJ102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ALBY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ALBY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="574" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="92">
   <si>
     <t>ALBY</t>
   </si>
@@ -656,173 +656,177 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43100</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43008</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42916</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>39721</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>39629</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E8" s="3">
         <v>3100</v>
-      </c>
-      <c r="E8" s="3">
-        <v>3000</v>
       </c>
       <c r="F8" s="3">
         <v>3000</v>
       </c>
       <c r="G8" s="3">
-        <v>2900</v>
+        <v>3000</v>
       </c>
       <c r="H8" s="3">
         <v>2800</v>
@@ -831,52 +835,52 @@
         <v>2800</v>
       </c>
       <c r="J8" s="3">
+        <v>2800</v>
+      </c>
+      <c r="K8" s="3">
         <v>3000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2900</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M8" s="3">
+      <c r="M8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N8" s="3">
         <v>2400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1600</v>
       </c>
-      <c r="P8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q8" s="3">
+      <c r="Q8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R8" s="3">
         <v>1800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1800</v>
-      </c>
-      <c r="T8" s="3">
-        <v>1700</v>
       </c>
       <c r="U8" s="3">
         <v>1700</v>
       </c>
       <c r="V8" s="3">
+        <v>1700</v>
+      </c>
+      <c r="W8" s="3">
         <v>1800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1700</v>
       </c>
-      <c r="X8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y8" s="3">
-        <v>0</v>
+      <c r="Y8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Z8" s="3">
         <v>0</v>
@@ -890,8 +894,8 @@
       <c r="AC8" s="3">
         <v>0</v>
       </c>
-      <c r="AD8" s="3" t="s">
-        <v>4</v>
+      <c r="AD8" s="3">
+        <v>0</v>
       </c>
       <c r="AE8" s="3" t="s">
         <v>4</v>
@@ -908,14 +912,17 @@
       <c r="AI8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AJ8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK8" s="3">
         <v>2400</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>2600</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -1021,22 +1028,25 @@
       <c r="AK9" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AL9" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E10" s="3">
         <v>3100</v>
-      </c>
-      <c r="E10" s="3">
-        <v>3000</v>
       </c>
       <c r="F10" s="3">
         <v>3000</v>
       </c>
       <c r="G10" s="3">
-        <v>2900</v>
+        <v>3000</v>
       </c>
       <c r="H10" s="3">
         <v>2800</v>
@@ -1045,14 +1055,14 @@
         <v>2800</v>
       </c>
       <c r="J10" s="3">
+        <v>2800</v>
+      </c>
+      <c r="K10" s="3">
         <v>3000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2900</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>4</v>
       </c>
@@ -1128,8 +1138,11 @@
       <c r="AK10" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AL10" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1167,8 +1180,9 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1274,8 +1288,11 @@
       <c r="AK12" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AL12" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1381,8 +1398,11 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1410,8 +1430,8 @@
       <c r="K14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1488,8 +1508,11 @@
       <c r="AK14" s="3">
         <v>0</v>
       </c>
+      <c r="AL14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1577,8 +1600,8 @@
       <c r="AE15" s="3">
         <v>0</v>
       </c>
-      <c r="AF15" s="3" t="s">
-        <v>4</v>
+      <c r="AF15" s="3">
+        <v>0</v>
       </c>
       <c r="AG15" s="3" t="s">
         <v>4</v>
@@ -1595,8 +1618,11 @@
       <c r="AK15" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AL15" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1631,16 +1657,17 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E17" s="3">
         <v>1700</v>
-      </c>
-      <c r="E17" s="3">
-        <v>1500</v>
       </c>
       <c r="F17" s="3">
         <v>1500</v>
@@ -1649,10 +1676,10 @@
         <v>1500</v>
       </c>
       <c r="H17" s="3">
+        <v>1500</v>
+      </c>
+      <c r="I17" s="3">
         <v>1600</v>
-      </c>
-      <c r="I17" s="3">
-        <v>1500</v>
       </c>
       <c r="J17" s="3">
         <v>1500</v>
@@ -1661,7 +1688,7 @@
         <v>1500</v>
       </c>
       <c r="L17" s="3">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="M17" s="3">
         <v>0</v>
@@ -1678,8 +1705,8 @@
       <c r="Q17" s="3">
         <v>0</v>
       </c>
-      <c r="R17" s="3" t="s">
-        <v>4</v>
+      <c r="R17" s="3">
+        <v>0</v>
       </c>
       <c r="S17" s="3" t="s">
         <v>4</v>
@@ -1696,8 +1723,8 @@
       <c r="W17" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X17" s="3">
-        <v>0</v>
+      <c r="X17" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Y17" s="3">
         <v>0</v>
@@ -1714,8 +1741,8 @@
       <c r="AC17" s="3">
         <v>0</v>
       </c>
-      <c r="AD17" s="3" t="s">
-        <v>4</v>
+      <c r="AD17" s="3">
+        <v>0</v>
       </c>
       <c r="AE17" s="3" t="s">
         <v>4</v>
@@ -1732,62 +1759,65 @@
       <c r="AI17" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AJ17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK17" s="3">
         <v>3700</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E18" s="3">
         <v>1400</v>
-      </c>
-      <c r="E18" s="3">
-        <v>1500</v>
       </c>
       <c r="F18" s="3">
         <v>1500</v>
       </c>
       <c r="G18" s="3">
-        <v>1400</v>
+        <v>1500</v>
       </c>
       <c r="H18" s="3">
+        <v>1300</v>
+      </c>
+      <c r="I18" s="3">
         <v>1200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1300</v>
-      </c>
-      <c r="J18" s="3">
-        <v>1400</v>
       </c>
       <c r="K18" s="3">
         <v>1400</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M18" s="3">
+      <c r="L18" s="3">
+        <v>1400</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N18" s="3">
         <v>2400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1600</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q18" s="3">
+      <c r="Q18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R18" s="3">
         <v>1800</v>
       </c>
-      <c r="R18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S18" s="3" t="s">
         <v>4</v>
       </c>
@@ -1806,8 +1836,8 @@
       <c r="X18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y18" s="3">
-        <v>0</v>
+      <c r="Y18" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Z18" s="3">
         <v>0</v>
@@ -1821,8 +1851,8 @@
       <c r="AC18" s="3">
         <v>0</v>
       </c>
-      <c r="AD18" s="3" t="s">
-        <v>4</v>
+      <c r="AD18" s="3">
+        <v>0</v>
       </c>
       <c r="AE18" s="3" t="s">
         <v>4</v>
@@ -1839,14 +1869,17 @@
       <c r="AI18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AJ18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK18" s="3">
         <v>-1300</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1884,8 +1917,9 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1916,23 +1950,23 @@
       <c r="L20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M20" s="3">
+      <c r="M20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N20" s="3">
         <v>-1400</v>
-      </c>
-      <c r="N20" s="3">
-        <v>-1100</v>
       </c>
       <c r="O20" s="3">
         <v>-1100</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q20" s="3">
+      <c r="P20" s="3">
         <v>-1100</v>
       </c>
-      <c r="R20" s="3" t="s">
-        <v>4</v>
+      <c r="Q20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R20" s="3">
+        <v>-1100</v>
       </c>
       <c r="S20" s="3" t="s">
         <v>4</v>
@@ -1952,8 +1986,8 @@
       <c r="X20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y20" s="3">
-        <v>500</v>
+      <c r="Y20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Z20" s="3">
         <v>500</v>
@@ -1967,8 +2001,8 @@
       <c r="AC20" s="3">
         <v>500</v>
       </c>
-      <c r="AD20" s="3" t="s">
-        <v>4</v>
+      <c r="AD20" s="3">
+        <v>500</v>
       </c>
       <c r="AE20" s="3" t="s">
         <v>4</v>
@@ -1985,43 +2019,46 @@
       <c r="AI20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AJ20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK20" s="3">
         <v>-3400</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-1700</v>
       </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E21" s="3">
         <v>1400</v>
-      </c>
-      <c r="E21" s="3">
-        <v>1500</v>
       </c>
       <c r="F21" s="3">
         <v>1500</v>
       </c>
       <c r="G21" s="3">
-        <v>1400</v>
+        <v>1500</v>
       </c>
       <c r="H21" s="3">
+        <v>1300</v>
+      </c>
+      <c r="I21" s="3">
         <v>1200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1300</v>
-      </c>
-      <c r="J21" s="3">
-        <v>1400</v>
       </c>
       <c r="K21" s="3">
         <v>1400</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>4</v>
+      <c r="L21" s="3">
+        <v>1400</v>
       </c>
       <c r="M21" s="3" t="s">
         <v>4</v>
@@ -2098,8 +2135,11 @@
       <c r="AK21" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AL21" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2127,8 +2167,8 @@
       <c r="K22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -2205,31 +2245,34 @@
       <c r="AK22" s="3">
         <v>0</v>
       </c>
+      <c r="AL22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E23" s="3">
         <v>1400</v>
-      </c>
-      <c r="E23" s="3">
-        <v>1500</v>
       </c>
       <c r="F23" s="3">
         <v>1500</v>
       </c>
       <c r="G23" s="3">
-        <v>1400</v>
+        <v>1500</v>
       </c>
       <c r="H23" s="3">
+        <v>1300</v>
+      </c>
+      <c r="I23" s="3">
         <v>1200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1300</v>
-      </c>
-      <c r="J23" s="3">
-        <v>1400</v>
       </c>
       <c r="K23" s="3">
         <v>1400</v>
@@ -2238,43 +2281,43 @@
         <v>1400</v>
       </c>
       <c r="M23" s="3">
+        <v>1400</v>
+      </c>
+      <c r="N23" s="3">
         <v>1000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>2500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>300</v>
-      </c>
-      <c r="Y23" s="3">
-        <v>500</v>
       </c>
       <c r="Z23" s="3">
         <v>500</v>
@@ -2289,39 +2332,42 @@
         <v>500</v>
       </c>
       <c r="AD23" s="3">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="AE23" s="3">
         <v>300</v>
       </c>
       <c r="AF23" s="3">
+        <v>300</v>
+      </c>
+      <c r="AG23" s="3">
         <v>400</v>
       </c>
-      <c r="AG23" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AH23" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AI23" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AJ23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK23" s="3">
         <v>-4700</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>400</v>
+      </c>
+      <c r="E24" s="3">
         <v>200</v>
-      </c>
-      <c r="E24" s="3">
-        <v>400</v>
       </c>
       <c r="F24" s="3">
         <v>400</v>
@@ -2336,37 +2382,37 @@
         <v>300</v>
       </c>
       <c r="J24" s="3">
+        <v>300</v>
+      </c>
+      <c r="K24" s="3">
         <v>400</v>
-      </c>
-      <c r="K24" s="3">
-        <v>300</v>
       </c>
       <c r="L24" s="3">
         <v>300</v>
       </c>
       <c r="M24" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="N24" s="3">
         <v>200</v>
       </c>
       <c r="O24" s="3">
+        <v>200</v>
+      </c>
+      <c r="P24" s="3">
         <v>100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>600</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>100</v>
       </c>
       <c r="R24" s="3">
         <v>100</v>
       </c>
       <c r="S24" s="3">
+        <v>100</v>
+      </c>
+      <c r="T24" s="3">
         <v>200</v>
-      </c>
-      <c r="T24" s="3">
-        <v>100</v>
       </c>
       <c r="U24" s="3">
         <v>100</v>
@@ -2402,25 +2448,28 @@
         <v>100</v>
       </c>
       <c r="AF24" s="3">
+        <v>100</v>
+      </c>
+      <c r="AG24" s="3">
         <v>2500</v>
       </c>
-      <c r="AG24" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AH24" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AI24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AJ24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK24" s="3">
         <v>-1600</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2526,16 +2575,19 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E26" s="3">
         <v>1200</v>
-      </c>
-      <c r="E26" s="3">
-        <v>1100</v>
       </c>
       <c r="F26" s="3">
         <v>1100</v>
@@ -2544,58 +2596,58 @@
         <v>1100</v>
       </c>
       <c r="H26" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I26" s="3">
         <v>900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1000</v>
-      </c>
-      <c r="J26" s="3">
-        <v>1100</v>
       </c>
       <c r="K26" s="3">
         <v>1100</v>
       </c>
-      <c r="L26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M26" s="3">
+      <c r="L26" s="3">
+        <v>1100</v>
+      </c>
+      <c r="M26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N26" s="3">
         <v>800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>400</v>
       </c>
-      <c r="P26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q26" s="3">
+      <c r="Q26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R26" s="3">
         <v>500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>600</v>
-      </c>
-      <c r="T26" s="3">
-        <v>400</v>
       </c>
       <c r="U26" s="3">
         <v>400</v>
       </c>
       <c r="V26" s="3">
+        <v>400</v>
+      </c>
+      <c r="W26" s="3">
         <v>500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>400</v>
       </c>
-      <c r="X26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y26" s="3">
-        <v>0</v>
+      <c r="Y26" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Z26" s="3">
         <v>0</v>
@@ -2609,8 +2661,8 @@
       <c r="AC26" s="3">
         <v>0</v>
       </c>
-      <c r="AD26" s="3" t="s">
-        <v>4</v>
+      <c r="AD26" s="3">
+        <v>0</v>
       </c>
       <c r="AE26" s="3" t="s">
         <v>4</v>
@@ -2627,22 +2679,25 @@
       <c r="AI26" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AJ26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK26" s="3">
         <v>-3100</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E27" s="3">
         <v>1200</v>
-      </c>
-      <c r="E27" s="3">
-        <v>1100</v>
       </c>
       <c r="F27" s="3">
         <v>1100</v>
@@ -2651,58 +2706,58 @@
         <v>1100</v>
       </c>
       <c r="H27" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I27" s="3">
         <v>900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1000</v>
-      </c>
-      <c r="J27" s="3">
-        <v>1100</v>
       </c>
       <c r="K27" s="3">
         <v>1100</v>
       </c>
-      <c r="L27" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M27" s="3">
+      <c r="L27" s="3">
+        <v>1100</v>
+      </c>
+      <c r="M27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N27" s="3">
         <v>800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>400</v>
       </c>
-      <c r="P27" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q27" s="3">
+      <c r="Q27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R27" s="3">
         <v>500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>600</v>
-      </c>
-      <c r="T27" s="3">
-        <v>400</v>
       </c>
       <c r="U27" s="3">
         <v>400</v>
       </c>
       <c r="V27" s="3">
+        <v>400</v>
+      </c>
+      <c r="W27" s="3">
         <v>500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>400</v>
       </c>
-      <c r="X27" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y27" s="3">
-        <v>0</v>
+      <c r="Y27" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Z27" s="3">
         <v>0</v>
@@ -2716,8 +2771,8 @@
       <c r="AC27" s="3">
         <v>0</v>
       </c>
-      <c r="AD27" s="3" t="s">
-        <v>4</v>
+      <c r="AD27" s="3">
+        <v>0</v>
       </c>
       <c r="AE27" s="3" t="s">
         <v>4</v>
@@ -2734,14 +2789,17 @@
       <c r="AI27" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AJ27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK27" s="3">
         <v>-3100</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2847,8 +2905,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2954,8 +3015,11 @@
       <c r="AK29" s="3">
         <v>0</v>
       </c>
+      <c r="AL29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3061,8 +3125,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3168,8 +3235,11 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3200,23 +3270,23 @@
       <c r="L32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M32" s="3">
+      <c r="M32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N32" s="3">
         <v>1400</v>
-      </c>
-      <c r="N32" s="3">
-        <v>1100</v>
       </c>
       <c r="O32" s="3">
         <v>1100</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q32" s="3">
+      <c r="P32" s="3">
         <v>1100</v>
       </c>
-      <c r="R32" s="3" t="s">
-        <v>4</v>
+      <c r="Q32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R32" s="3">
+        <v>1100</v>
       </c>
       <c r="S32" s="3" t="s">
         <v>4</v>
@@ -3236,8 +3306,8 @@
       <c r="X32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y32" s="3">
-        <v>-500</v>
+      <c r="Y32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Z32" s="3">
         <v>-500</v>
@@ -3251,8 +3321,8 @@
       <c r="AC32" s="3">
         <v>-500</v>
       </c>
-      <c r="AD32" s="3" t="s">
-        <v>4</v>
+      <c r="AD32" s="3">
+        <v>-500</v>
       </c>
       <c r="AE32" s="3" t="s">
         <v>4</v>
@@ -3269,22 +3339,25 @@
       <c r="AI32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AJ32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK32" s="3">
         <v>3400</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E33" s="3">
         <v>1200</v>
-      </c>
-      <c r="E33" s="3">
-        <v>1100</v>
       </c>
       <c r="F33" s="3">
         <v>1100</v>
@@ -3293,58 +3366,58 @@
         <v>1100</v>
       </c>
       <c r="H33" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I33" s="3">
         <v>900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1000</v>
-      </c>
-      <c r="J33" s="3">
-        <v>1100</v>
       </c>
       <c r="K33" s="3">
         <v>1100</v>
       </c>
-      <c r="L33" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M33" s="3">
+      <c r="L33" s="3">
+        <v>1100</v>
+      </c>
+      <c r="M33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N33" s="3">
         <v>800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>400</v>
       </c>
-      <c r="P33" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q33" s="3">
+      <c r="Q33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R33" s="3">
         <v>500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>600</v>
-      </c>
-      <c r="T33" s="3">
-        <v>400</v>
       </c>
       <c r="U33" s="3">
         <v>400</v>
       </c>
       <c r="V33" s="3">
+        <v>400</v>
+      </c>
+      <c r="W33" s="3">
         <v>500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>400</v>
       </c>
-      <c r="X33" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y33" s="3">
-        <v>0</v>
+      <c r="Y33" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Z33" s="3">
         <v>0</v>
@@ -3358,8 +3431,8 @@
       <c r="AC33" s="3">
         <v>0</v>
       </c>
-      <c r="AD33" s="3" t="s">
-        <v>4</v>
+      <c r="AD33" s="3">
+        <v>0</v>
       </c>
       <c r="AE33" s="3" t="s">
         <v>4</v>
@@ -3376,14 +3449,17 @@
       <c r="AI33" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AJ33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK33" s="3">
         <v>-3100</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3489,16 +3565,19 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E35" s="3">
         <v>1200</v>
-      </c>
-      <c r="E35" s="3">
-        <v>1100</v>
       </c>
       <c r="F35" s="3">
         <v>1100</v>
@@ -3507,58 +3586,58 @@
         <v>1100</v>
       </c>
       <c r="H35" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I35" s="3">
         <v>900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1000</v>
-      </c>
-      <c r="J35" s="3">
-        <v>1100</v>
       </c>
       <c r="K35" s="3">
         <v>1100</v>
       </c>
-      <c r="L35" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M35" s="3">
+      <c r="L35" s="3">
+        <v>1100</v>
+      </c>
+      <c r="M35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N35" s="3">
         <v>800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>400</v>
       </c>
-      <c r="P35" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q35" s="3">
+      <c r="Q35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R35" s="3">
         <v>500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>600</v>
-      </c>
-      <c r="T35" s="3">
-        <v>400</v>
       </c>
       <c r="U35" s="3">
         <v>400</v>
       </c>
       <c r="V35" s="3">
+        <v>400</v>
+      </c>
+      <c r="W35" s="3">
         <v>500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>400</v>
       </c>
-      <c r="X35" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y35" s="3">
-        <v>0</v>
+      <c r="Y35" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Z35" s="3">
         <v>0</v>
@@ -3572,8 +3651,8 @@
       <c r="AC35" s="3">
         <v>0</v>
       </c>
-      <c r="AD35" s="3" t="s">
-        <v>4</v>
+      <c r="AD35" s="3">
+        <v>0</v>
       </c>
       <c r="AE35" s="3" t="s">
         <v>4</v>
@@ -3590,126 +3669,132 @@
       <c r="AI35" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AJ35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK35" s="3">
         <v>-3100</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43100</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43008</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42916</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>39721</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>39629</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3747,8 +3832,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3786,8 +3872,9 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -3815,8 +3902,8 @@
       <c r="K41" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L41" s="3">
-        <v>0</v>
+      <c r="L41" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M41" s="3">
         <v>0</v>
@@ -3888,13 +3975,16 @@
         <v>0</v>
       </c>
       <c r="AJ41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK41" s="3">
         <v>4100</v>
       </c>
-      <c r="AK41" s="3" t="s">
+      <c r="AL41" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3995,13 +4085,16 @@
         <v>0</v>
       </c>
       <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK42" s="3">
         <v>900</v>
       </c>
-      <c r="AK42" s="3" t="s">
+      <c r="AL42" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -4029,8 +4122,8 @@
       <c r="K43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L43" s="3">
-        <v>0</v>
+      <c r="L43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M43" s="3">
         <v>0</v>
@@ -4107,8 +4200,11 @@
       <c r="AK43" s="3">
         <v>0</v>
       </c>
+      <c r="AL43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4136,8 +4232,8 @@
       <c r="K44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -4214,8 +4310,11 @@
       <c r="AK44" s="3">
         <v>0</v>
       </c>
+      <c r="AL44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4243,8 +4342,8 @@
       <c r="K45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L45" s="3">
-        <v>0</v>
+      <c r="L45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M45" s="3">
         <v>0</v>
@@ -4321,8 +4420,11 @@
       <c r="AK45" s="3">
         <v>0</v>
       </c>
+      <c r="AL45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -4350,8 +4452,8 @@
       <c r="K46" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L46" s="3">
-        <v>0</v>
+      <c r="L46" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M46" s="3">
         <v>0</v>
@@ -4428,8 +4530,11 @@
       <c r="AK46" s="3">
         <v>0</v>
       </c>
+      <c r="AL46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4457,8 +4562,8 @@
       <c r="K47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -4535,8 +4640,11 @@
       <c r="AK47" s="3">
         <v>0</v>
       </c>
+      <c r="AL47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4564,8 +4672,8 @@
       <c r="K48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L48" s="3">
-        <v>0</v>
+      <c r="L48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M48" s="3">
         <v>0</v>
@@ -4637,13 +4745,16 @@
         <v>0</v>
       </c>
       <c r="AJ48" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK48" s="3">
         <v>6400</v>
       </c>
-      <c r="AK48" s="3" t="s">
+      <c r="AL48" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4744,13 +4855,16 @@
         <v>0</v>
       </c>
       <c r="AJ49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK49" s="3">
         <v>2500</v>
       </c>
-      <c r="AK49" s="3" t="s">
+      <c r="AL49" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4856,8 +4970,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4963,8 +5080,11 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4992,8 +5112,8 @@
       <c r="K52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L52" s="3">
-        <v>0</v>
+      <c r="L52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M52" s="3">
         <v>0</v>
@@ -5070,8 +5190,11 @@
       <c r="AK52" s="3">
         <v>0</v>
       </c>
+      <c r="AL52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5177,8 +5300,11 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
@@ -5206,8 +5332,8 @@
       <c r="K54" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L54" s="3">
-        <v>0</v>
+      <c r="L54" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M54" s="3">
         <v>0</v>
@@ -5279,13 +5405,16 @@
         <v>0</v>
       </c>
       <c r="AJ54" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK54" s="3">
         <v>198900</v>
       </c>
-      <c r="AK54" s="3" t="s">
+      <c r="AL54" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5323,8 +5452,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5362,8 +5492,9 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -5391,8 +5522,8 @@
       <c r="K57" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L57" s="3">
-        <v>0</v>
+      <c r="L57" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M57" s="3">
         <v>0</v>
@@ -5469,8 +5600,11 @@
       <c r="AK57" s="3">
         <v>0</v>
       </c>
+      <c r="AL57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5576,8 +5710,11 @@
       <c r="AK58" s="3">
         <v>0</v>
       </c>
+      <c r="AL58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5605,8 +5742,8 @@
       <c r="K59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L59" s="3">
-        <v>0</v>
+      <c r="L59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M59" s="3">
         <v>0</v>
@@ -5683,8 +5820,11 @@
       <c r="AK59" s="3">
         <v>0</v>
       </c>
+      <c r="AL59" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5712,8 +5852,8 @@
       <c r="K60" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L60" s="3">
-        <v>0</v>
+      <c r="L60" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M60" s="3">
         <v>0</v>
@@ -5790,8 +5930,11 @@
       <c r="AK60" s="3">
         <v>0</v>
       </c>
+      <c r="AL60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5897,8 +6040,11 @@
       <c r="AK61" s="3">
         <v>0</v>
       </c>
+      <c r="AL61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5926,8 +6072,8 @@
       <c r="K62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L62" s="3">
-        <v>0</v>
+      <c r="L62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M62" s="3">
         <v>0</v>
@@ -6004,8 +6150,11 @@
       <c r="AK62" s="3">
         <v>0</v>
       </c>
+      <c r="AL62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6111,8 +6260,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6218,8 +6370,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6325,8 +6480,11 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
@@ -6354,8 +6512,8 @@
       <c r="K66" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L66" s="3">
-        <v>0</v>
+      <c r="L66" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M66" s="3">
         <v>0</v>
@@ -6427,13 +6585,16 @@
         <v>0</v>
       </c>
       <c r="AJ66" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK66" s="3">
         <v>177800</v>
       </c>
-      <c r="AK66" s="3" t="s">
+      <c r="AL66" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6471,8 +6632,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6578,8 +6740,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6685,8 +6850,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6792,8 +6960,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6899,8 +7070,11 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -6928,8 +7102,8 @@
       <c r="K72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L72" s="3">
-        <v>0</v>
+      <c r="L72" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M72" s="3">
         <v>0</v>
@@ -7006,8 +7180,11 @@
       <c r="AK72" s="3">
         <v>0</v>
       </c>
+      <c r="AL72" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7113,8 +7290,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7220,8 +7400,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7327,8 +7510,11 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
@@ -7356,45 +7542,45 @@
       <c r="K76" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L76" s="3">
+      <c r="L76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M76" s="3">
         <v>20800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>21000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>20500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>20400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>19100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>19600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>19100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>18600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>17000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>16800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>17100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>16600</v>
       </c>
-      <c r="X76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y76" s="3" t="s">
         <v>4</v>
       </c>
@@ -7407,8 +7593,8 @@
       <c r="AB76" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC76" s="3">
-        <v>0</v>
+      <c r="AC76" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AD76" s="3">
         <v>0</v>
@@ -7429,13 +7615,16 @@
         <v>0</v>
       </c>
       <c r="AJ76" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK76" s="3">
         <v>21100</v>
       </c>
-      <c r="AK76" s="3" t="s">
+      <c r="AL76" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7541,128 +7730,134 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43100</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43008</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42916</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>39721</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>39629</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E81" s="3">
         <v>1200</v>
-      </c>
-      <c r="E81" s="3">
-        <v>1100</v>
       </c>
       <c r="F81" s="3">
         <v>1100</v>
@@ -7671,58 +7866,58 @@
         <v>1100</v>
       </c>
       <c r="H81" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I81" s="3">
         <v>900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1000</v>
-      </c>
-      <c r="J81" s="3">
-        <v>1100</v>
       </c>
       <c r="K81" s="3">
         <v>1100</v>
       </c>
-      <c r="L81" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M81" s="3">
+      <c r="L81" s="3">
+        <v>1100</v>
+      </c>
+      <c r="M81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N81" s="3">
         <v>800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>400</v>
       </c>
-      <c r="P81" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q81" s="3">
+      <c r="Q81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R81" s="3">
         <v>500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>600</v>
-      </c>
-      <c r="T81" s="3">
-        <v>400</v>
       </c>
       <c r="U81" s="3">
         <v>400</v>
       </c>
       <c r="V81" s="3">
+        <v>400</v>
+      </c>
+      <c r="W81" s="3">
         <v>500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>400</v>
       </c>
-      <c r="X81" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y81" s="3">
-        <v>0</v>
+      <c r="Y81" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Z81" s="3">
         <v>0</v>
@@ -7736,8 +7931,8 @@
       <c r="AC81" s="3">
         <v>0</v>
       </c>
-      <c r="AD81" s="3" t="s">
-        <v>4</v>
+      <c r="AD81" s="3">
+        <v>0</v>
       </c>
       <c r="AE81" s="3" t="s">
         <v>4</v>
@@ -7754,14 +7949,17 @@
       <c r="AI81" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AJ81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK81" s="3">
         <v>-3100</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7799,8 +7997,9 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7828,8 +8027,8 @@
       <c r="K83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L83" s="3">
-        <v>0</v>
+      <c r="L83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M83" s="3">
         <v>0</v>
@@ -7906,8 +8105,11 @@
       <c r="AK83" s="3">
         <v>0</v>
       </c>
+      <c r="AL83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8013,8 +8215,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8120,8 +8325,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8227,8 +8435,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8334,8 +8545,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8441,8 +8655,11 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -8470,8 +8687,8 @@
       <c r="K89" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L89" s="3">
-        <v>0</v>
+      <c r="L89" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M89" s="3">
         <v>0</v>
@@ -8548,8 +8765,11 @@
       <c r="AK89" s="3">
         <v>0</v>
       </c>
+      <c r="AL89" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8587,8 +8807,9 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8616,8 +8837,8 @@
       <c r="K91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
+      <c r="L91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M91" s="3">
         <v>0</v>
@@ -8694,8 +8915,11 @@
       <c r="AK91" s="3">
         <v>0</v>
       </c>
+      <c r="AL91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8801,8 +9025,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8908,8 +9135,11 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -8937,8 +9167,8 @@
       <c r="K94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
+      <c r="L94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M94" s="3">
         <v>0</v>
@@ -9015,8 +9245,11 @@
       <c r="AK94" s="3">
         <v>0</v>
       </c>
+      <c r="AL94" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9054,8 +9287,9 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9083,8 +9317,8 @@
       <c r="K96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -9161,8 +9395,11 @@
       <c r="AK96" s="3">
         <v>0</v>
       </c>
+      <c r="AL96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9268,8 +9505,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9375,8 +9615,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9482,8 +9725,11 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -9511,8 +9757,8 @@
       <c r="K100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
+      <c r="L100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M100" s="3">
         <v>0</v>
@@ -9589,8 +9835,11 @@
       <c r="AK100" s="3">
         <v>0</v>
       </c>
+      <c r="AL100" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9618,8 +9867,8 @@
       <c r="K101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -9696,8 +9945,11 @@
       <c r="AK101" s="3">
         <v>0</v>
       </c>
+      <c r="AL101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -9725,8 +9977,8 @@
       <c r="K102" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L102" s="3">
-        <v>0</v>
+      <c r="L102" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M102" s="3">
         <v>0</v>
@@ -9801,6 +10053,9 @@
         <v>0</v>
       </c>
       <c r="AK102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ALBY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ALBY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="737" uniqueCount="92">
   <si>
     <t>ALBY</t>
   </si>
@@ -816,26 +816,26 @@
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3">
-        <v>3000</v>
-      </c>
-      <c r="E8" s="3">
-        <v>3100</v>
-      </c>
-      <c r="F8" s="3">
-        <v>3000</v>
-      </c>
-      <c r="G8" s="3">
-        <v>3000</v>
-      </c>
-      <c r="H8" s="3">
-        <v>2800</v>
-      </c>
-      <c r="I8" s="3">
-        <v>2800</v>
-      </c>
-      <c r="J8" s="3">
-        <v>2800</v>
+      <c r="D8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K8" s="3">
         <v>3000</v>
@@ -1036,26 +1036,26 @@
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3">
-        <v>3000</v>
-      </c>
-      <c r="E10" s="3">
-        <v>3100</v>
-      </c>
-      <c r="F10" s="3">
-        <v>3000</v>
-      </c>
-      <c r="G10" s="3">
-        <v>3000</v>
-      </c>
-      <c r="H10" s="3">
-        <v>2800</v>
-      </c>
-      <c r="I10" s="3">
-        <v>2800</v>
-      </c>
-      <c r="J10" s="3">
-        <v>2800</v>
+      <c r="D10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K10" s="3">
         <v>3000</v>
@@ -1516,26 +1516,26 @@
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3">
-        <v>0</v>
-      </c>
-      <c r="E15" s="3">
-        <v>0</v>
-      </c>
-      <c r="F15" s="3">
-        <v>0</v>
-      </c>
-      <c r="G15" s="3">
-        <v>0</v>
-      </c>
-      <c r="H15" s="3">
-        <v>0</v>
-      </c>
-      <c r="I15" s="3">
-        <v>0</v>
-      </c>
-      <c r="J15" s="3">
-        <v>0</v>
+      <c r="D15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1663,26 +1663,26 @@
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3">
-        <v>1500</v>
-      </c>
-      <c r="E17" s="3">
-        <v>1700</v>
-      </c>
-      <c r="F17" s="3">
-        <v>1500</v>
-      </c>
-      <c r="G17" s="3">
-        <v>1500</v>
-      </c>
-      <c r="H17" s="3">
-        <v>1500</v>
-      </c>
-      <c r="I17" s="3">
-        <v>1600</v>
-      </c>
-      <c r="J17" s="3">
-        <v>1500</v>
+      <c r="D17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K17" s="3">
         <v>1500</v>
@@ -1773,26 +1773,26 @@
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
-        <v>1500</v>
-      </c>
-      <c r="E18" s="3">
-        <v>1400</v>
-      </c>
-      <c r="F18" s="3">
-        <v>1500</v>
-      </c>
-      <c r="G18" s="3">
-        <v>1500</v>
-      </c>
-      <c r="H18" s="3">
-        <v>1300</v>
-      </c>
-      <c r="I18" s="3">
-        <v>1200</v>
-      </c>
-      <c r="J18" s="3">
-        <v>1300</v>
+      <c r="D18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K18" s="3">
         <v>1400</v>
@@ -2033,26 +2033,26 @@
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3">
-        <v>1500</v>
-      </c>
-      <c r="E21" s="3">
-        <v>1400</v>
-      </c>
-      <c r="F21" s="3">
-        <v>1500</v>
-      </c>
-      <c r="G21" s="3">
-        <v>1500</v>
-      </c>
-      <c r="H21" s="3">
-        <v>1300</v>
-      </c>
-      <c r="I21" s="3">
-        <v>1200</v>
-      </c>
-      <c r="J21" s="3">
-        <v>1300</v>
+      <c r="D21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K21" s="3">
         <v>1400</v>
@@ -2253,26 +2253,26 @@
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3">
-        <v>1500</v>
-      </c>
-      <c r="E23" s="3">
-        <v>1400</v>
-      </c>
-      <c r="F23" s="3">
-        <v>1500</v>
-      </c>
-      <c r="G23" s="3">
-        <v>1500</v>
-      </c>
-      <c r="H23" s="3">
-        <v>1300</v>
-      </c>
-      <c r="I23" s="3">
-        <v>1200</v>
-      </c>
-      <c r="J23" s="3">
-        <v>1300</v>
+      <c r="D23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K23" s="3">
         <v>1400</v>
@@ -2363,26 +2363,26 @@
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>400</v>
-      </c>
-      <c r="E24" s="3">
-        <v>200</v>
-      </c>
-      <c r="F24" s="3">
-        <v>400</v>
-      </c>
-      <c r="G24" s="3">
-        <v>400</v>
-      </c>
-      <c r="H24" s="3">
-        <v>300</v>
-      </c>
-      <c r="I24" s="3">
-        <v>300</v>
-      </c>
-      <c r="J24" s="3">
-        <v>300</v>
+      <c r="D24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K24" s="3">
         <v>400</v>
@@ -2583,26 +2583,26 @@
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
-        <v>1100</v>
-      </c>
-      <c r="E26" s="3">
-        <v>1200</v>
-      </c>
-      <c r="F26" s="3">
-        <v>1100</v>
-      </c>
-      <c r="G26" s="3">
-        <v>1100</v>
-      </c>
-      <c r="H26" s="3">
-        <v>1000</v>
-      </c>
-      <c r="I26" s="3">
-        <v>900</v>
-      </c>
-      <c r="J26" s="3">
-        <v>1000</v>
+      <c r="D26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K26" s="3">
         <v>1100</v>
@@ -2693,26 +2693,26 @@
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
-        <v>1100</v>
-      </c>
-      <c r="E27" s="3">
-        <v>1200</v>
-      </c>
-      <c r="F27" s="3">
-        <v>1100</v>
-      </c>
-      <c r="G27" s="3">
-        <v>1100</v>
-      </c>
-      <c r="H27" s="3">
-        <v>1000</v>
-      </c>
-      <c r="I27" s="3">
-        <v>900</v>
-      </c>
-      <c r="J27" s="3">
-        <v>1000</v>
+      <c r="D27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K27" s="3">
         <v>1100</v>
@@ -2913,26 +2913,26 @@
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3">
-        <v>0</v>
-      </c>
-      <c r="E29" s="3">
-        <v>0</v>
-      </c>
-      <c r="F29" s="3">
-        <v>0</v>
-      </c>
-      <c r="G29" s="3">
-        <v>0</v>
-      </c>
-      <c r="H29" s="3">
-        <v>0</v>
-      </c>
-      <c r="I29" s="3">
-        <v>0</v>
-      </c>
-      <c r="J29" s="3">
-        <v>0</v>
+      <c r="D29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K29" s="3">
         <v>0</v>
@@ -3353,26 +3353,26 @@
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
-        <v>1100</v>
-      </c>
-      <c r="E33" s="3">
-        <v>1200</v>
-      </c>
-      <c r="F33" s="3">
-        <v>1100</v>
-      </c>
-      <c r="G33" s="3">
-        <v>1100</v>
-      </c>
-      <c r="H33" s="3">
-        <v>1000</v>
-      </c>
-      <c r="I33" s="3">
-        <v>900</v>
-      </c>
-      <c r="J33" s="3">
-        <v>1000</v>
+      <c r="D33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K33" s="3">
         <v>1100</v>
@@ -3573,26 +3573,26 @@
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
-        <v>1100</v>
-      </c>
-      <c r="E35" s="3">
-        <v>1200</v>
-      </c>
-      <c r="F35" s="3">
-        <v>1100</v>
-      </c>
-      <c r="G35" s="3">
-        <v>1100</v>
-      </c>
-      <c r="H35" s="3">
-        <v>1000</v>
-      </c>
-      <c r="I35" s="3">
-        <v>900</v>
-      </c>
-      <c r="J35" s="3">
-        <v>1000</v>
+      <c r="D35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K35" s="3">
         <v>1100</v>
@@ -3988,26 +3988,26 @@
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D42" s="3">
-        <v>0</v>
-      </c>
-      <c r="E42" s="3">
-        <v>0</v>
-      </c>
-      <c r="F42" s="3">
-        <v>0</v>
-      </c>
-      <c r="G42" s="3">
-        <v>0</v>
-      </c>
-      <c r="H42" s="3">
-        <v>0</v>
-      </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
-      <c r="J42" s="3">
-        <v>0</v>
+      <c r="D42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K42" s="3">
         <v>0</v>
@@ -4758,26 +4758,26 @@
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3">
-        <v>0</v>
-      </c>
-      <c r="E49" s="3">
-        <v>0</v>
-      </c>
-      <c r="F49" s="3">
-        <v>0</v>
-      </c>
-      <c r="G49" s="3">
-        <v>0</v>
-      </c>
-      <c r="H49" s="3">
-        <v>0</v>
-      </c>
-      <c r="I49" s="3">
-        <v>0</v>
-      </c>
-      <c r="J49" s="3">
-        <v>0</v>
+      <c r="D49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K49" s="3">
         <v>0</v>
@@ -5608,26 +5608,26 @@
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3">
-        <v>0</v>
-      </c>
-      <c r="E58" s="3">
-        <v>0</v>
-      </c>
-      <c r="F58" s="3">
-        <v>0</v>
-      </c>
-      <c r="G58" s="3">
-        <v>0</v>
-      </c>
-      <c r="H58" s="3">
-        <v>0</v>
-      </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
-      <c r="J58" s="3">
-        <v>0</v>
+      <c r="D58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -5938,26 +5938,26 @@
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D61" s="3">
-        <v>0</v>
-      </c>
-      <c r="E61" s="3">
-        <v>0</v>
-      </c>
-      <c r="F61" s="3">
-        <v>0</v>
-      </c>
-      <c r="G61" s="3">
-        <v>0</v>
-      </c>
-      <c r="H61" s="3">
-        <v>0</v>
-      </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
-      <c r="J61" s="3">
-        <v>0</v>
+      <c r="D61" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G61" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H61" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I61" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J61" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -6858,26 +6858,26 @@
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="D70" s="3">
-        <v>0</v>
-      </c>
-      <c r="E70" s="3">
-        <v>0</v>
-      </c>
-      <c r="F70" s="3">
-        <v>0</v>
-      </c>
-      <c r="G70" s="3">
-        <v>0</v>
-      </c>
-      <c r="H70" s="3">
-        <v>0</v>
-      </c>
-      <c r="I70" s="3">
-        <v>0</v>
-      </c>
-      <c r="J70" s="3">
-        <v>0</v>
+      <c r="D70" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E70" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F70" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H70" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I70" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J70" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K70" s="3">
         <v>0</v>
@@ -7853,26 +7853,26 @@
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
-        <v>1100</v>
-      </c>
-      <c r="E81" s="3">
-        <v>1200</v>
-      </c>
-      <c r="F81" s="3">
-        <v>1100</v>
-      </c>
-      <c r="G81" s="3">
-        <v>1100</v>
-      </c>
-      <c r="H81" s="3">
-        <v>1000</v>
-      </c>
-      <c r="I81" s="3">
-        <v>900</v>
-      </c>
-      <c r="J81" s="3">
-        <v>1000</v>
+      <c r="D81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J81" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K81" s="3">
         <v>1100</v>

--- a/AAII_Financials/Quarterly/ALBY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ALBY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="737" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="92">
   <si>
     <t>ALBY</t>
   </si>
@@ -656,234 +656,237 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
-        <v>45657</v>
-      </c>
       <c r="F7" s="2">
-        <v>45565</v>
+        <v>43830</v>
       </c>
       <c r="G7" s="2">
-        <v>45473</v>
+        <v>43465</v>
       </c>
       <c r="H7" s="2">
-        <v>45382</v>
+        <v>39355</v>
       </c>
       <c r="I7" s="2">
-        <v>45291</v>
+        <v>39263</v>
       </c>
       <c r="J7" s="2">
+        <v>39172</v>
+      </c>
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43100</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43008</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42825</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>39721</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>39629</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K8" s="3">
+      <c r="D8" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E8" s="3">
         <v>3000</v>
       </c>
+      <c r="F8" s="3">
+        <v>2000</v>
+      </c>
+      <c r="G8" s="3">
+        <v>1800</v>
+      </c>
+      <c r="H8" s="3">
+        <v>1600</v>
+      </c>
+      <c r="I8" s="3">
+        <v>2200</v>
+      </c>
+      <c r="J8" s="3">
+        <v>2700</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>4</v>
+      </c>
       <c r="L8" s="3">
+        <v>3000</v>
+      </c>
+      <c r="M8" s="3">
         <v>2900</v>
       </c>
-      <c r="M8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N8" s="3">
+      <c r="N8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O8" s="3">
         <v>2400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1600</v>
       </c>
-      <c r="Q8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R8" s="3">
+      <c r="R8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S8" s="3">
         <v>1800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1800</v>
-      </c>
-      <c r="U8" s="3">
-        <v>1700</v>
       </c>
       <c r="V8" s="3">
         <v>1700</v>
       </c>
       <c r="W8" s="3">
+        <v>1700</v>
+      </c>
+      <c r="X8" s="3">
         <v>1800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1700</v>
       </c>
-      <c r="Y8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z8" s="3">
-        <v>0</v>
+      <c r="Z8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AA8" s="3">
         <v>0</v>
@@ -897,8 +900,8 @@
       <c r="AD8" s="3">
         <v>0</v>
       </c>
-      <c r="AE8" s="3" t="s">
-        <v>4</v>
+      <c r="AE8" s="3">
+        <v>0</v>
       </c>
       <c r="AF8" s="3" t="s">
         <v>4</v>
@@ -915,14 +918,17 @@
       <c r="AJ8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AK8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL8" s="3">
         <v>2400</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>2600</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -1031,41 +1037,44 @@
       <c r="AL9" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AM9" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K10" s="3">
+      <c r="D10" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E10" s="3">
         <v>3000</v>
       </c>
+      <c r="F10" s="3">
+        <v>2000</v>
+      </c>
+      <c r="G10" s="3">
+        <v>1800</v>
+      </c>
+      <c r="H10" s="3">
+        <v>1600</v>
+      </c>
+      <c r="I10" s="3">
+        <v>2200</v>
+      </c>
+      <c r="J10" s="3">
+        <v>2700</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>4</v>
+      </c>
       <c r="L10" s="3">
+        <v>3000</v>
+      </c>
+      <c r="M10" s="3">
         <v>2900</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N10" s="3" t="s">
         <v>4</v>
       </c>
@@ -1141,8 +1150,11 @@
       <c r="AL10" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AM10" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1181,8 +1193,9 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1291,8 +1304,11 @@
       <c r="AL12" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AM12" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1401,8 +1417,11 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1418,11 +1437,11 @@
       <c r="G14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>4</v>
+      <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
+        <v>-200</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>4</v>
@@ -1433,8 +1452,8 @@
       <c r="L14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -1511,34 +1530,37 @@
       <c r="AL14" s="3">
         <v>0</v>
       </c>
+      <c r="AM14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K15" s="3">
-        <v>0</v>
+      <c r="D15" s="3">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
+        <v>0</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="3">
+        <v>100</v>
+      </c>
+      <c r="I15" s="3">
+        <v>100</v>
+      </c>
+      <c r="J15" s="3">
+        <v>100</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L15" s="3">
         <v>0</v>
@@ -1603,8 +1625,8 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-      <c r="AG15" s="3" t="s">
-        <v>4</v>
+      <c r="AG15" s="3">
+        <v>0</v>
       </c>
       <c r="AH15" s="3" t="s">
         <v>4</v>
@@ -1621,8 +1643,11 @@
       <c r="AL15" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AM15" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1658,40 +1683,41 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K17" s="3">
+      <c r="D17" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E17" s="3">
         <v>1500</v>
+      </c>
+      <c r="F17" s="3">
+        <v>1600</v>
+      </c>
+      <c r="G17" s="3">
+        <v>1200</v>
+      </c>
+      <c r="H17" s="3">
+        <v>2300</v>
+      </c>
+      <c r="I17" s="3">
+        <v>2300</v>
+      </c>
+      <c r="J17" s="3">
+        <v>2100</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L17" s="3">
         <v>1500</v>
       </c>
       <c r="M17" s="3">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="N17" s="3">
         <v>0</v>
@@ -1708,8 +1734,8 @@
       <c r="R17" s="3">
         <v>0</v>
       </c>
-      <c r="S17" s="3" t="s">
-        <v>4</v>
+      <c r="S17" s="3">
+        <v>0</v>
       </c>
       <c r="T17" s="3" t="s">
         <v>4</v>
@@ -1726,8 +1752,8 @@
       <c r="X17" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y17" s="3">
-        <v>0</v>
+      <c r="Y17" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Z17" s="3">
         <v>0</v>
@@ -1744,8 +1770,8 @@
       <c r="AD17" s="3">
         <v>0</v>
       </c>
-      <c r="AE17" s="3" t="s">
-        <v>4</v>
+      <c r="AE17" s="3">
+        <v>0</v>
       </c>
       <c r="AF17" s="3" t="s">
         <v>4</v>
@@ -1762,65 +1788,68 @@
       <c r="AJ17" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AK17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL17" s="3">
         <v>3700</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K18" s="3">
-        <v>1400</v>
+      <c r="D18" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E18" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F18" s="3">
+        <v>400</v>
+      </c>
+      <c r="G18" s="3">
+        <v>600</v>
+      </c>
+      <c r="H18" s="3">
+        <v>-700</v>
+      </c>
+      <c r="I18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J18" s="3">
+        <v>600</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L18" s="3">
         <v>1400</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N18" s="3">
+      <c r="M18" s="3">
+        <v>1400</v>
+      </c>
+      <c r="N18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O18" s="3">
         <v>2400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1600</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R18" s="3">
+      <c r="R18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S18" s="3">
         <v>1800</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T18" s="3" t="s">
         <v>4</v>
       </c>
@@ -1839,8 +1868,8 @@
       <c r="Y18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z18" s="3">
-        <v>0</v>
+      <c r="Z18" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AA18" s="3">
         <v>0</v>
@@ -1854,8 +1883,8 @@
       <c r="AD18" s="3">
         <v>0</v>
       </c>
-      <c r="AE18" s="3" t="s">
-        <v>4</v>
+      <c r="AE18" s="3">
+        <v>0</v>
       </c>
       <c r="AF18" s="3" t="s">
         <v>4</v>
@@ -1872,14 +1901,17 @@
       <c r="AJ18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AK18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL18" s="3">
         <v>-1300</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1918,8 +1950,9 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1929,20 +1962,20 @@
       <c r="E20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>4</v>
+      <c r="F20" s="3">
+        <v>100</v>
+      </c>
+      <c r="G20" s="3">
+        <v>100</v>
+      </c>
+      <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
+        <v>0</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>4</v>
@@ -1953,23 +1986,23 @@
       <c r="M20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N20" s="3">
+      <c r="N20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O20" s="3">
         <v>-1400</v>
-      </c>
-      <c r="O20" s="3">
-        <v>-1100</v>
       </c>
       <c r="P20" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R20" s="3">
+      <c r="Q20" s="3">
         <v>-1100</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>4</v>
+      <c r="R20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S20" s="3">
+        <v>-1100</v>
       </c>
       <c r="T20" s="3" t="s">
         <v>4</v>
@@ -1989,8 +2022,8 @@
       <c r="Y20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z20" s="3">
-        <v>500</v>
+      <c r="Z20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AA20" s="3">
         <v>500</v>
@@ -2004,8 +2037,8 @@
       <c r="AD20" s="3">
         <v>500</v>
       </c>
-      <c r="AE20" s="3" t="s">
-        <v>4</v>
+      <c r="AE20" s="3">
+        <v>500</v>
       </c>
       <c r="AF20" s="3" t="s">
         <v>4</v>
@@ -2022,46 +2055,49 @@
       <c r="AJ20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AK20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL20" s="3">
         <v>-3400</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-1700</v>
       </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K21" s="3">
-        <v>1400</v>
+      <c r="D21" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E21" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F21" s="3">
+        <v>400</v>
+      </c>
+      <c r="G21" s="3">
+        <v>500</v>
+      </c>
+      <c r="H21" s="3">
+        <v>-600</v>
+      </c>
+      <c r="I21" s="3">
+        <v>0</v>
+      </c>
+      <c r="J21" s="3">
+        <v>700</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L21" s="3">
         <v>1400</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>4</v>
+      <c r="M21" s="3">
+        <v>1400</v>
       </c>
       <c r="N21" s="3" t="s">
         <v>4</v>
@@ -2138,8 +2174,11 @@
       <c r="AL21" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AM21" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2170,8 +2209,8 @@
       <c r="L22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -2248,34 +2287,37 @@
       <c r="AL22" s="3">
         <v>0</v>
       </c>
+      <c r="AM22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K23" s="3">
-        <v>1400</v>
+      <c r="D23" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E23" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F23" s="3">
+        <v>300</v>
+      </c>
+      <c r="G23" s="3">
+        <v>500</v>
+      </c>
+      <c r="H23" s="3">
+        <v>-700</v>
+      </c>
+      <c r="I23" s="3">
+        <v>100</v>
+      </c>
+      <c r="J23" s="3">
+        <v>600</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L23" s="3">
         <v>1400</v>
@@ -2284,43 +2326,43 @@
         <v>1400</v>
       </c>
       <c r="N23" s="3">
+        <v>1400</v>
+      </c>
+      <c r="O23" s="3">
         <v>1000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>2500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>300</v>
-      </c>
-      <c r="Z23" s="3">
-        <v>500</v>
       </c>
       <c r="AA23" s="3">
         <v>500</v>
@@ -2335,87 +2377,90 @@
         <v>500</v>
       </c>
       <c r="AE23" s="3">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="AF23" s="3">
         <v>300</v>
       </c>
       <c r="AG23" s="3">
+        <v>300</v>
+      </c>
+      <c r="AH23" s="3">
         <v>400</v>
       </c>
-      <c r="AH23" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AI23" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AJ23" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AK23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL23" s="3">
         <v>-4700</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K24" s="3">
+      <c r="D24" s="3">
         <v>400</v>
       </c>
+      <c r="E24" s="3">
+        <v>400</v>
+      </c>
+      <c r="F24" s="3">
+        <v>100</v>
+      </c>
+      <c r="G24" s="3">
+        <v>100</v>
+      </c>
+      <c r="H24" s="3">
+        <v>-300</v>
+      </c>
+      <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3">
+        <v>200</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>4</v>
+      </c>
       <c r="L24" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="M24" s="3">
         <v>300</v>
       </c>
       <c r="N24" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="O24" s="3">
         <v>200</v>
       </c>
       <c r="P24" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q24" s="3">
         <v>100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>600</v>
-      </c>
-      <c r="R24" s="3">
-        <v>100</v>
       </c>
       <c r="S24" s="3">
         <v>100</v>
       </c>
       <c r="T24" s="3">
+        <v>100</v>
+      </c>
+      <c r="U24" s="3">
         <v>200</v>
-      </c>
-      <c r="U24" s="3">
-        <v>100</v>
       </c>
       <c r="V24" s="3">
         <v>100</v>
@@ -2451,25 +2496,28 @@
         <v>100</v>
       </c>
       <c r="AG24" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH24" s="3">
         <v>2500</v>
       </c>
-      <c r="AH24" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AI24" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AJ24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AK24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL24" s="3">
         <v>-1600</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2578,79 +2626,82 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K26" s="3">
+      <c r="D26" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E26" s="3">
         <v>1100</v>
+      </c>
+      <c r="F26" s="3">
+        <v>300</v>
+      </c>
+      <c r="G26" s="3">
+        <v>400</v>
+      </c>
+      <c r="H26" s="3">
+        <v>-400</v>
+      </c>
+      <c r="I26" s="3">
+        <v>100</v>
+      </c>
+      <c r="J26" s="3">
+        <v>400</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L26" s="3">
         <v>1100</v>
       </c>
-      <c r="M26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N26" s="3">
+      <c r="M26" s="3">
+        <v>1100</v>
+      </c>
+      <c r="N26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O26" s="3">
         <v>800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>400</v>
       </c>
-      <c r="Q26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R26" s="3">
+      <c r="R26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S26" s="3">
         <v>500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>600</v>
-      </c>
-      <c r="U26" s="3">
-        <v>400</v>
       </c>
       <c r="V26" s="3">
         <v>400</v>
       </c>
       <c r="W26" s="3">
+        <v>400</v>
+      </c>
+      <c r="X26" s="3">
         <v>500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>400</v>
       </c>
-      <c r="Y26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z26" s="3">
-        <v>0</v>
+      <c r="Z26" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AA26" s="3">
         <v>0</v>
@@ -2664,8 +2715,8 @@
       <c r="AD26" s="3">
         <v>0</v>
       </c>
-      <c r="AE26" s="3" t="s">
-        <v>4</v>
+      <c r="AE26" s="3">
+        <v>0</v>
       </c>
       <c r="AF26" s="3" t="s">
         <v>4</v>
@@ -2682,85 +2733,88 @@
       <c r="AJ26" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AK26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL26" s="3">
         <v>-3100</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K27" s="3">
+      <c r="D27" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E27" s="3">
         <v>1100</v>
+      </c>
+      <c r="F27" s="3">
+        <v>300</v>
+      </c>
+      <c r="G27" s="3">
+        <v>400</v>
+      </c>
+      <c r="H27" s="3">
+        <v>-400</v>
+      </c>
+      <c r="I27" s="3">
+        <v>100</v>
+      </c>
+      <c r="J27" s="3">
+        <v>400</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L27" s="3">
         <v>1100</v>
       </c>
-      <c r="M27" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N27" s="3">
+      <c r="M27" s="3">
+        <v>1100</v>
+      </c>
+      <c r="N27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O27" s="3">
         <v>800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>400</v>
       </c>
-      <c r="Q27" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R27" s="3">
+      <c r="R27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S27" s="3">
         <v>500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>600</v>
-      </c>
-      <c r="U27" s="3">
-        <v>400</v>
       </c>
       <c r="V27" s="3">
         <v>400</v>
       </c>
       <c r="W27" s="3">
+        <v>400</v>
+      </c>
+      <c r="X27" s="3">
         <v>500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>400</v>
       </c>
-      <c r="Y27" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z27" s="3">
-        <v>0</v>
+      <c r="Z27" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AA27" s="3">
         <v>0</v>
@@ -2774,8 +2828,8 @@
       <c r="AD27" s="3">
         <v>0</v>
       </c>
-      <c r="AE27" s="3" t="s">
-        <v>4</v>
+      <c r="AE27" s="3">
+        <v>0</v>
       </c>
       <c r="AF27" s="3" t="s">
         <v>4</v>
@@ -2792,14 +2846,17 @@
       <c r="AJ27" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AK27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL27" s="3">
         <v>-3100</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2908,34 +2965,37 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K29" s="3">
-        <v>0</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L29" s="3">
         <v>0</v>
@@ -3018,8 +3078,11 @@
       <c r="AL29" s="3">
         <v>0</v>
       </c>
+      <c r="AM29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3128,8 +3191,11 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3238,8 +3304,11 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3249,20 +3318,20 @@
       <c r="E32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>4</v>
+      <c r="F32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="G32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
+        <v>0</v>
       </c>
       <c r="K32" s="3" t="s">
         <v>4</v>
@@ -3273,23 +3342,23 @@
       <c r="M32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N32" s="3">
+      <c r="N32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O32" s="3">
         <v>1400</v>
-      </c>
-      <c r="O32" s="3">
-        <v>1100</v>
       </c>
       <c r="P32" s="3">
         <v>1100</v>
       </c>
-      <c r="Q32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R32" s="3">
+      <c r="Q32" s="3">
         <v>1100</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>4</v>
+      <c r="R32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S32" s="3">
+        <v>1100</v>
       </c>
       <c r="T32" s="3" t="s">
         <v>4</v>
@@ -3309,8 +3378,8 @@
       <c r="Y32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z32" s="3">
-        <v>-500</v>
+      <c r="Z32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AA32" s="3">
         <v>-500</v>
@@ -3324,8 +3393,8 @@
       <c r="AD32" s="3">
         <v>-500</v>
       </c>
-      <c r="AE32" s="3" t="s">
-        <v>4</v>
+      <c r="AE32" s="3">
+        <v>-500</v>
       </c>
       <c r="AF32" s="3" t="s">
         <v>4</v>
@@ -3342,85 +3411,88 @@
       <c r="AJ32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AK32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL32" s="3">
         <v>3400</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I33" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J33" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K33" s="3">
+      <c r="D33" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E33" s="3">
         <v>1100</v>
+      </c>
+      <c r="F33" s="3">
+        <v>300</v>
+      </c>
+      <c r="G33" s="3">
+        <v>400</v>
+      </c>
+      <c r="H33" s="3">
+        <v>-400</v>
+      </c>
+      <c r="I33" s="3">
+        <v>100</v>
+      </c>
+      <c r="J33" s="3">
+        <v>400</v>
+      </c>
+      <c r="K33" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L33" s="3">
         <v>1100</v>
       </c>
-      <c r="M33" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N33" s="3">
+      <c r="M33" s="3">
+        <v>1100</v>
+      </c>
+      <c r="N33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O33" s="3">
         <v>800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>400</v>
       </c>
-      <c r="Q33" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R33" s="3">
+      <c r="R33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S33" s="3">
         <v>500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>600</v>
-      </c>
-      <c r="U33" s="3">
-        <v>400</v>
       </c>
       <c r="V33" s="3">
         <v>400</v>
       </c>
       <c r="W33" s="3">
+        <v>400</v>
+      </c>
+      <c r="X33" s="3">
         <v>500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>400</v>
       </c>
-      <c r="Y33" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z33" s="3">
-        <v>0</v>
+      <c r="Z33" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AA33" s="3">
         <v>0</v>
@@ -3434,8 +3506,8 @@
       <c r="AD33" s="3">
         <v>0</v>
       </c>
-      <c r="AE33" s="3" t="s">
-        <v>4</v>
+      <c r="AE33" s="3">
+        <v>0</v>
       </c>
       <c r="AF33" s="3" t="s">
         <v>4</v>
@@ -3452,14 +3524,17 @@
       <c r="AJ33" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AK33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL33" s="3">
         <v>-3100</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3568,79 +3643,82 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J35" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K35" s="3">
+      <c r="D35" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E35" s="3">
         <v>1100</v>
+      </c>
+      <c r="F35" s="3">
+        <v>300</v>
+      </c>
+      <c r="G35" s="3">
+        <v>400</v>
+      </c>
+      <c r="H35" s="3">
+        <v>-400</v>
+      </c>
+      <c r="I35" s="3">
+        <v>100</v>
+      </c>
+      <c r="J35" s="3">
+        <v>400</v>
+      </c>
+      <c r="K35" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L35" s="3">
         <v>1100</v>
       </c>
-      <c r="M35" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N35" s="3">
+      <c r="M35" s="3">
+        <v>1100</v>
+      </c>
+      <c r="N35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O35" s="3">
         <v>800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>400</v>
       </c>
-      <c r="Q35" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R35" s="3">
+      <c r="R35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S35" s="3">
         <v>500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>600</v>
-      </c>
-      <c r="U35" s="3">
-        <v>400</v>
       </c>
       <c r="V35" s="3">
         <v>400</v>
       </c>
       <c r="W35" s="3">
+        <v>400</v>
+      </c>
+      <c r="X35" s="3">
         <v>500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>400</v>
       </c>
-      <c r="Y35" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z35" s="3">
-        <v>0</v>
+      <c r="Z35" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AA35" s="3">
         <v>0</v>
@@ -3654,8 +3732,8 @@
       <c r="AD35" s="3">
         <v>0</v>
       </c>
-      <c r="AE35" s="3" t="s">
-        <v>4</v>
+      <c r="AE35" s="3">
+        <v>0</v>
       </c>
       <c r="AF35" s="3" t="s">
         <v>4</v>
@@ -3672,129 +3750,135 @@
       <c r="AJ35" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AK35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL35" s="3">
         <v>-3100</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
-        <v>45657</v>
-      </c>
       <c r="F38" s="2">
-        <v>45565</v>
+        <v>43830</v>
       </c>
       <c r="G38" s="2">
-        <v>45473</v>
+        <v>43465</v>
       </c>
       <c r="H38" s="2">
-        <v>45382</v>
+        <v>39355</v>
       </c>
       <c r="I38" s="2">
-        <v>45291</v>
+        <v>39263</v>
       </c>
       <c r="J38" s="2">
+        <v>39172</v>
+      </c>
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43100</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43008</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42825</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>39721</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>39629</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3833,8 +3917,9 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3873,8 +3958,9 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -3884,20 +3970,20 @@
       <c r="E41" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J41" s="3" t="s">
-        <v>4</v>
+      <c r="F41" s="3">
+        <v>23500</v>
+      </c>
+      <c r="G41" s="3">
+        <v>28000</v>
+      </c>
+      <c r="H41" s="3">
+        <v>26900</v>
+      </c>
+      <c r="I41" s="3">
+        <v>30700</v>
+      </c>
+      <c r="J41" s="3">
+        <v>16100</v>
       </c>
       <c r="K41" s="3" t="s">
         <v>4</v>
@@ -3905,8 +3991,8 @@
       <c r="L41" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M41" s="3">
-        <v>0</v>
+      <c r="M41" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N41" s="3">
         <v>0</v>
@@ -3978,39 +4064,42 @@
         <v>0</v>
       </c>
       <c r="AK41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL41" s="3">
         <v>4100</v>
       </c>
-      <c r="AL41" s="3" t="s">
+      <c r="AM41" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K42" s="3">
-        <v>0</v>
+      <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L42" s="3">
         <v>0</v>
@@ -4088,13 +4177,16 @@
         <v>0</v>
       </c>
       <c r="AK42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL42" s="3">
         <v>900</v>
       </c>
-      <c r="AL42" s="3" t="s">
+      <c r="AM42" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -4125,8 +4217,8 @@
       <c r="L43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M43" s="3">
-        <v>0</v>
+      <c r="M43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N43" s="3">
         <v>0</v>
@@ -4203,8 +4295,11 @@
       <c r="AL43" s="3">
         <v>0</v>
       </c>
+      <c r="AM43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4235,8 +4330,8 @@
       <c r="L44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -4313,8 +4408,11 @@
       <c r="AL44" s="3">
         <v>0</v>
       </c>
+      <c r="AM44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4324,11 +4422,11 @@
       <c r="E45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>4</v>
+      <c r="F45" s="3">
+        <v>500</v>
+      </c>
+      <c r="G45" s="3">
+        <v>500</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>4</v>
@@ -4345,8 +4443,8 @@
       <c r="L45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M45" s="3">
-        <v>0</v>
+      <c r="M45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N45" s="3">
         <v>0</v>
@@ -4423,8 +4521,11 @@
       <c r="AL45" s="3">
         <v>0</v>
       </c>
+      <c r="AM45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -4434,20 +4535,20 @@
       <c r="E46" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F46" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G46" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I46" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J46" s="3" t="s">
-        <v>4</v>
+      <c r="F46" s="3">
+        <v>26200</v>
+      </c>
+      <c r="G46" s="3">
+        <v>30500</v>
+      </c>
+      <c r="H46" s="3">
+        <v>26900</v>
+      </c>
+      <c r="I46" s="3">
+        <v>30700</v>
+      </c>
+      <c r="J46" s="3">
+        <v>16100</v>
       </c>
       <c r="K46" s="3" t="s">
         <v>4</v>
@@ -4455,8 +4556,8 @@
       <c r="L46" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M46" s="3">
-        <v>0</v>
+      <c r="M46" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N46" s="3">
         <v>0</v>
@@ -4533,8 +4634,11 @@
       <c r="AL46" s="3">
         <v>0</v>
       </c>
+      <c r="AM46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4544,20 +4648,20 @@
       <c r="E47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>4</v>
+      <c r="F47" s="3">
+        <v>1200</v>
+      </c>
+      <c r="G47" s="3">
+        <v>1700</v>
+      </c>
+      <c r="H47" s="3">
+        <v>51000</v>
+      </c>
+      <c r="I47" s="3">
+        <v>40800</v>
+      </c>
+      <c r="J47" s="3">
+        <v>37100</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>4</v>
@@ -4565,8 +4669,8 @@
       <c r="L47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -4643,8 +4747,11 @@
       <c r="AL47" s="3">
         <v>0</v>
       </c>
+      <c r="AM47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4654,20 +4761,20 @@
       <c r="E48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J48" s="3" t="s">
-        <v>4</v>
+      <c r="F48" s="3">
+        <v>2500</v>
+      </c>
+      <c r="G48" s="3">
+        <v>2500</v>
+      </c>
+      <c r="H48" s="3">
+        <v>6700</v>
+      </c>
+      <c r="I48" s="3">
+        <v>6700</v>
+      </c>
+      <c r="J48" s="3">
+        <v>6700</v>
       </c>
       <c r="K48" s="3" t="s">
         <v>4</v>
@@ -4675,8 +4782,8 @@
       <c r="L48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M48" s="3">
-        <v>0</v>
+      <c r="M48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N48" s="3">
         <v>0</v>
@@ -4748,39 +4855,42 @@
         <v>0</v>
       </c>
       <c r="AK48" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL48" s="3">
         <v>6400</v>
       </c>
-      <c r="AL48" s="3" t="s">
+      <c r="AM48" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K49" s="3">
-        <v>0</v>
+      <c r="D49" s="3">
+        <v>0</v>
+      </c>
+      <c r="E49" s="3">
+        <v>0</v>
+      </c>
+      <c r="F49" s="3">
+        <v>0</v>
+      </c>
+      <c r="G49" s="3">
+        <v>0</v>
+      </c>
+      <c r="H49" s="3">
+        <v>2500</v>
+      </c>
+      <c r="I49" s="3">
+        <v>2600</v>
+      </c>
+      <c r="J49" s="3">
+        <v>2600</v>
+      </c>
+      <c r="K49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L49" s="3">
         <v>0</v>
@@ -4858,13 +4968,16 @@
         <v>0</v>
       </c>
       <c r="AK49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL49" s="3">
         <v>2500</v>
       </c>
-      <c r="AL49" s="3" t="s">
+      <c r="AM49" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4973,8 +5086,11 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5083,8 +5199,11 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -5094,20 +5213,20 @@
       <c r="E52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>4</v>
+      <c r="F52" s="3">
+        <v>600</v>
+      </c>
+      <c r="G52" s="3">
+        <v>600</v>
+      </c>
+      <c r="H52" s="3">
+        <v>15400</v>
+      </c>
+      <c r="I52" s="3">
+        <v>15200</v>
+      </c>
+      <c r="J52" s="3">
+        <v>17900</v>
       </c>
       <c r="K52" s="3" t="s">
         <v>4</v>
@@ -5115,8 +5234,8 @@
       <c r="L52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M52" s="3">
-        <v>0</v>
+      <c r="M52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N52" s="3">
         <v>0</v>
@@ -5193,8 +5312,11 @@
       <c r="AL52" s="3">
         <v>0</v>
       </c>
+      <c r="AM52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5303,8 +5425,11 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
@@ -5314,20 +5439,20 @@
       <c r="E54" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J54" s="3" t="s">
-        <v>4</v>
+      <c r="F54" s="3">
+        <v>195600</v>
+      </c>
+      <c r="G54" s="3">
+        <v>194200</v>
+      </c>
+      <c r="H54" s="3">
+        <v>248800</v>
+      </c>
+      <c r="I54" s="3">
+        <v>266500</v>
+      </c>
+      <c r="J54" s="3">
+        <v>286900</v>
       </c>
       <c r="K54" s="3" t="s">
         <v>4</v>
@@ -5335,8 +5460,8 @@
       <c r="L54" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M54" s="3">
-        <v>0</v>
+      <c r="M54" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N54" s="3">
         <v>0</v>
@@ -5408,13 +5533,16 @@
         <v>0</v>
       </c>
       <c r="AK54" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL54" s="3">
         <v>198900</v>
       </c>
-      <c r="AL54" s="3" t="s">
+      <c r="AM54" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5453,8 +5581,9 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5493,8 +5622,9 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -5504,20 +5634,20 @@
       <c r="E57" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J57" s="3" t="s">
-        <v>4</v>
+      <c r="F57" s="3">
+        <v>156500</v>
+      </c>
+      <c r="G57" s="3">
+        <v>158700</v>
+      </c>
+      <c r="H57" s="3">
+        <v>190600</v>
+      </c>
+      <c r="I57" s="3">
+        <v>206600</v>
+      </c>
+      <c r="J57" s="3">
+        <v>226900</v>
       </c>
       <c r="K57" s="3" t="s">
         <v>4</v>
@@ -5525,8 +5655,8 @@
       <c r="L57" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M57" s="3">
-        <v>0</v>
+      <c r="M57" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N57" s="3">
         <v>0</v>
@@ -5603,34 +5733,37 @@
       <c r="AL57" s="3">
         <v>0</v>
       </c>
+      <c r="AM57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K58" s="3">
-        <v>0</v>
+      <c r="D58" s="3">
+        <v>0</v>
+      </c>
+      <c r="E58" s="3">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3">
+        <v>5900</v>
+      </c>
+      <c r="G58" s="3">
+        <v>0</v>
+      </c>
+      <c r="H58" s="3">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
+        <v>0</v>
+      </c>
+      <c r="K58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L58" s="3">
         <v>0</v>
@@ -5713,8 +5846,11 @@
       <c r="AL58" s="3">
         <v>0</v>
       </c>
+      <c r="AM58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5745,8 +5881,8 @@
       <c r="L59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M59" s="3">
-        <v>0</v>
+      <c r="M59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N59" s="3">
         <v>0</v>
@@ -5823,8 +5959,11 @@
       <c r="AL59" s="3">
         <v>0</v>
       </c>
+      <c r="AM59" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5834,20 +5973,20 @@
       <c r="E60" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J60" s="3" t="s">
-        <v>4</v>
+      <c r="F60" s="3">
+        <v>162400</v>
+      </c>
+      <c r="G60" s="3">
+        <v>158800</v>
+      </c>
+      <c r="H60" s="3">
+        <v>190600</v>
+      </c>
+      <c r="I60" s="3">
+        <v>206600</v>
+      </c>
+      <c r="J60" s="3">
+        <v>226900</v>
       </c>
       <c r="K60" s="3" t="s">
         <v>4</v>
@@ -5855,8 +5994,8 @@
       <c r="L60" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M60" s="3">
-        <v>0</v>
+      <c r="M60" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N60" s="3">
         <v>0</v>
@@ -5933,34 +6072,37 @@
       <c r="AL60" s="3">
         <v>0</v>
       </c>
+      <c r="AM60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D61" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E61" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F61" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G61" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H61" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I61" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J61" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K61" s="3">
-        <v>0</v>
+      <c r="D61" s="3">
+        <v>0</v>
+      </c>
+      <c r="E61" s="3">
+        <v>0</v>
+      </c>
+      <c r="F61" s="3">
+        <v>16500</v>
+      </c>
+      <c r="G61" s="3">
+        <v>20200</v>
+      </c>
+      <c r="H61" s="3">
+        <v>29100</v>
+      </c>
+      <c r="I61" s="3">
+        <v>31100</v>
+      </c>
+      <c r="J61" s="3">
+        <v>31100</v>
+      </c>
+      <c r="K61" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L61" s="3">
         <v>0</v>
@@ -6043,8 +6185,11 @@
       <c r="AL61" s="3">
         <v>0</v>
       </c>
+      <c r="AM61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -6054,20 +6199,20 @@
       <c r="E62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J62" s="3" t="s">
-        <v>4</v>
+      <c r="F62" s="3">
+        <v>600</v>
+      </c>
+      <c r="G62" s="3">
+        <v>500</v>
+      </c>
+      <c r="H62" s="3">
+        <v>2000</v>
+      </c>
+      <c r="I62" s="3">
+        <v>1500</v>
+      </c>
+      <c r="J62" s="3">
+        <v>1600</v>
       </c>
       <c r="K62" s="3" t="s">
         <v>4</v>
@@ -6075,8 +6220,8 @@
       <c r="L62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M62" s="3">
-        <v>0</v>
+      <c r="M62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N62" s="3">
         <v>0</v>
@@ -6153,8 +6298,11 @@
       <c r="AL62" s="3">
         <v>0</v>
       </c>
+      <c r="AM62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6263,8 +6411,11 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6373,8 +6524,11 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6483,8 +6637,11 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
@@ -6494,20 +6651,20 @@
       <c r="E66" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J66" s="3" t="s">
-        <v>4</v>
+      <c r="F66" s="3">
+        <v>179500</v>
+      </c>
+      <c r="G66" s="3">
+        <v>179500</v>
+      </c>
+      <c r="H66" s="3">
+        <v>221600</v>
+      </c>
+      <c r="I66" s="3">
+        <v>239200</v>
+      </c>
+      <c r="J66" s="3">
+        <v>259600</v>
       </c>
       <c r="K66" s="3" t="s">
         <v>4</v>
@@ -6515,8 +6672,8 @@
       <c r="L66" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M66" s="3">
-        <v>0</v>
+      <c r="M66" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N66" s="3">
         <v>0</v>
@@ -6588,13 +6745,16 @@
         <v>0</v>
       </c>
       <c r="AK66" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL66" s="3">
         <v>177800</v>
       </c>
-      <c r="AL66" s="3" t="s">
+      <c r="AM66" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6633,8 +6793,9 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6743,8 +6904,11 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6853,34 +7017,37 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="D70" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E70" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F70" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G70" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H70" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I70" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J70" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K70" s="3">
-        <v>0</v>
+      <c r="D70" s="3">
+        <v>0</v>
+      </c>
+      <c r="E70" s="3">
+        <v>0</v>
+      </c>
+      <c r="F70" s="3">
+        <v>0</v>
+      </c>
+      <c r="G70" s="3">
+        <v>0</v>
+      </c>
+      <c r="H70" s="3">
+        <v>0</v>
+      </c>
+      <c r="I70" s="3">
+        <v>0</v>
+      </c>
+      <c r="J70" s="3">
+        <v>0</v>
+      </c>
+      <c r="K70" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L70" s="3">
         <v>0</v>
@@ -6963,8 +7130,11 @@
       <c r="AL70" s="3">
         <v>0</v>
       </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7073,8 +7243,11 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -7084,20 +7257,20 @@
       <c r="E72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J72" s="3" t="s">
-        <v>4</v>
+      <c r="F72" s="3">
+        <v>-16100</v>
+      </c>
+      <c r="G72" s="3">
+        <v>-17500</v>
+      </c>
+      <c r="H72" s="3">
+        <v>1500</v>
+      </c>
+      <c r="I72" s="3">
+        <v>2000</v>
+      </c>
+      <c r="J72" s="3">
+        <v>2000</v>
       </c>
       <c r="K72" s="3" t="s">
         <v>4</v>
@@ -7105,8 +7278,8 @@
       <c r="L72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M72" s="3">
-        <v>0</v>
+      <c r="M72" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N72" s="3">
         <v>0</v>
@@ -7183,8 +7356,11 @@
       <c r="AL72" s="3">
         <v>0</v>
       </c>
+      <c r="AM72" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7293,8 +7469,11 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7403,8 +7582,11 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7513,8 +7695,11 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
@@ -7524,20 +7709,20 @@
       <c r="E76" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F76" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G76" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H76" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I76" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J76" s="3" t="s">
-        <v>4</v>
+      <c r="F76" s="3">
+        <v>16200</v>
+      </c>
+      <c r="G76" s="3">
+        <v>14700</v>
+      </c>
+      <c r="H76" s="3">
+        <v>27200</v>
+      </c>
+      <c r="I76" s="3">
+        <v>27300</v>
+      </c>
+      <c r="J76" s="3">
+        <v>27300</v>
       </c>
       <c r="K76" s="3" t="s">
         <v>4</v>
@@ -7545,45 +7730,45 @@
       <c r="L76" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M76" s="3">
+      <c r="M76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N76" s="3">
         <v>20800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>21000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>20500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>20400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>19100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>19600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>19100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>18600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>17000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>16800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>17100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>16600</v>
       </c>
-      <c r="Y76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z76" s="3" t="s">
         <v>4</v>
       </c>
@@ -7596,8 +7781,8 @@
       <c r="AC76" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AD76" s="3">
-        <v>0</v>
+      <c r="AD76" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AE76" s="3">
         <v>0</v>
@@ -7618,13 +7803,16 @@
         <v>0</v>
       </c>
       <c r="AK76" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL76" s="3">
         <v>21100</v>
       </c>
-      <c r="AL76" s="3" t="s">
+      <c r="AM76" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7733,194 +7921,200 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
-        <v>45657</v>
-      </c>
       <c r="F80" s="2">
-        <v>45565</v>
+        <v>43830</v>
       </c>
       <c r="G80" s="2">
-        <v>45473</v>
+        <v>43465</v>
       </c>
       <c r="H80" s="2">
-        <v>45382</v>
+        <v>39355</v>
       </c>
       <c r="I80" s="2">
-        <v>45291</v>
+        <v>39263</v>
       </c>
       <c r="J80" s="2">
+        <v>39172</v>
+      </c>
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43100</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43008</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42825</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>39721</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>39629</v>
       </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E81" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F81" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G81" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H81" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I81" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J81" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K81" s="3">
+      <c r="D81" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E81" s="3">
         <v>1100</v>
+      </c>
+      <c r="F81" s="3">
+        <v>300</v>
+      </c>
+      <c r="G81" s="3">
+        <v>400</v>
+      </c>
+      <c r="H81" s="3">
+        <v>-400</v>
+      </c>
+      <c r="I81" s="3">
+        <v>100</v>
+      </c>
+      <c r="J81" s="3">
+        <v>400</v>
+      </c>
+      <c r="K81" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L81" s="3">
         <v>1100</v>
       </c>
-      <c r="M81" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N81" s="3">
+      <c r="M81" s="3">
+        <v>1100</v>
+      </c>
+      <c r="N81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O81" s="3">
         <v>800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>400</v>
       </c>
-      <c r="Q81" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R81" s="3">
+      <c r="R81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S81" s="3">
         <v>500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>600</v>
-      </c>
-      <c r="U81" s="3">
-        <v>400</v>
       </c>
       <c r="V81" s="3">
         <v>400</v>
       </c>
       <c r="W81" s="3">
+        <v>400</v>
+      </c>
+      <c r="X81" s="3">
         <v>500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>400</v>
       </c>
-      <c r="Y81" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z81" s="3">
-        <v>0</v>
+      <c r="Z81" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AA81" s="3">
         <v>0</v>
@@ -7934,8 +8128,8 @@
       <c r="AD81" s="3">
         <v>0</v>
       </c>
-      <c r="AE81" s="3" t="s">
-        <v>4</v>
+      <c r="AE81" s="3">
+        <v>0</v>
       </c>
       <c r="AF81" s="3" t="s">
         <v>4</v>
@@ -7952,14 +8146,17 @@
       <c r="AJ81" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AK81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL81" s="3">
         <v>-3100</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7998,31 +8195,32 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J83" s="3" t="s">
-        <v>4</v>
+      <c r="D83" s="3">
+        <v>100</v>
+      </c>
+      <c r="E83" s="3">
+        <v>100</v>
+      </c>
+      <c r="F83" s="3">
+        <v>100</v>
+      </c>
+      <c r="G83" s="3">
+        <v>100</v>
+      </c>
+      <c r="H83" s="3">
+        <v>100</v>
+      </c>
+      <c r="I83" s="3">
+        <v>100</v>
+      </c>
+      <c r="J83" s="3">
+        <v>100</v>
       </c>
       <c r="K83" s="3" t="s">
         <v>4</v>
@@ -8030,8 +8228,8 @@
       <c r="L83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M83" s="3">
-        <v>0</v>
+      <c r="M83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N83" s="3">
         <v>0</v>
@@ -8108,8 +8306,11 @@
       <c r="AL83" s="3">
         <v>0</v>
       </c>
+      <c r="AM83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8218,8 +8419,11 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8328,8 +8532,11 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8438,8 +8645,11 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8548,8 +8758,11 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8658,8 +8871,11 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -8675,14 +8891,14 @@
       <c r="G89" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J89" s="3" t="s">
-        <v>4</v>
+      <c r="H89" s="3">
+        <v>400</v>
+      </c>
+      <c r="I89" s="3">
+        <v>-600</v>
+      </c>
+      <c r="J89" s="3">
+        <v>400</v>
       </c>
       <c r="K89" s="3" t="s">
         <v>4</v>
@@ -8690,8 +8906,8 @@
       <c r="L89" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M89" s="3">
-        <v>0</v>
+      <c r="M89" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N89" s="3">
         <v>0</v>
@@ -8768,8 +8984,11 @@
       <c r="AL89" s="3">
         <v>0</v>
       </c>
+      <c r="AM89" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8808,8 +9027,9 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8825,14 +9045,14 @@
       <c r="G91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J91" s="3" t="s">
-        <v>4</v>
+      <c r="H91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J91" s="3">
+        <v>0</v>
       </c>
       <c r="K91" s="3" t="s">
         <v>4</v>
@@ -8840,8 +9060,8 @@
       <c r="L91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
+      <c r="M91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N91" s="3">
         <v>0</v>
@@ -8918,8 +9138,11 @@
       <c r="AL91" s="3">
         <v>0</v>
       </c>
+      <c r="AM91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9028,8 +9251,11 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9138,8 +9364,11 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -9155,14 +9384,14 @@
       <c r="G94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J94" s="3" t="s">
-        <v>4</v>
+      <c r="H94" s="3">
+        <v>20000</v>
+      </c>
+      <c r="I94" s="3">
+        <v>14600</v>
+      </c>
+      <c r="J94" s="3">
+        <v>14100</v>
       </c>
       <c r="K94" s="3" t="s">
         <v>4</v>
@@ -9170,8 +9399,8 @@
       <c r="L94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
+      <c r="M94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N94" s="3">
         <v>0</v>
@@ -9248,8 +9477,11 @@
       <c r="AL94" s="3">
         <v>0</v>
       </c>
+      <c r="AM94" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9288,8 +9520,9 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9305,14 +9538,14 @@
       <c r="G96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J96" s="3" t="s">
-        <v>4</v>
+      <c r="H96" s="3">
+        <v>100</v>
+      </c>
+      <c r="I96" s="3">
+        <v>100</v>
+      </c>
+      <c r="J96" s="3">
+        <v>100</v>
       </c>
       <c r="K96" s="3" t="s">
         <v>4</v>
@@ -9320,8 +9553,8 @@
       <c r="L96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -9398,8 +9631,11 @@
       <c r="AL96" s="3">
         <v>0</v>
       </c>
+      <c r="AM96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9508,8 +9744,11 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9618,8 +9857,11 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9728,8 +9970,11 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -9745,14 +9990,14 @@
       <c r="G100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J100" s="3" t="s">
-        <v>4</v>
+      <c r="H100" s="3">
+        <v>-18100</v>
+      </c>
+      <c r="I100" s="3">
+        <v>-20100</v>
+      </c>
+      <c r="J100" s="3">
+        <v>-10700</v>
       </c>
       <c r="K100" s="3" t="s">
         <v>4</v>
@@ -9760,8 +10005,8 @@
       <c r="L100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
+      <c r="M100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N100" s="3">
         <v>0</v>
@@ -9838,8 +10083,11 @@
       <c r="AL100" s="3">
         <v>0</v>
       </c>
+      <c r="AM100" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9870,8 +10118,8 @@
       <c r="L101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -9948,31 +10196,34 @@
       <c r="AL101" s="3">
         <v>0</v>
       </c>
+      <c r="AM101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J102" s="3" t="s">
-        <v>4</v>
+      <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
+        <v>0</v>
+      </c>
+      <c r="H102" s="3">
+        <v>2300</v>
+      </c>
+      <c r="I102" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="J102" s="3">
+        <v>3800</v>
       </c>
       <c r="K102" s="3" t="s">
         <v>4</v>
@@ -9980,8 +10231,8 @@
       <c r="L102" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M102" s="3">
-        <v>0</v>
+      <c r="M102" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N102" s="3">
         <v>0</v>
@@ -10056,6 +10307,9 @@
         <v>0</v>
       </c>
       <c r="AL102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM102" s="3">
         <v>0</v>
       </c>
     </row>
